--- a/data_tables/guide_text.xlsx
+++ b/data_tables/guide_text.xlsx
@@ -14,6 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranges" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EquipTypes" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClassMetadata" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClassProfiles" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillDescriptions" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,93 +444,88 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>readme_title</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t># Dungeon Travelers 2-2 Reference Guide (Vanilla)</t>
+          <t>classes_intro</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reference documentation for the original English PC release of Dungeon Travelers 2-2. All data and formulas are extracted directly from the game executable (DT22_en_unwrapped.exe) and packaged archive files.</t>
+          <t>Classes are organized into five base lines across three tiers: Base (Tier 1), Intermediate (Tier 2, Level 15), and Advanced (Tier 3, Level 30). Six Advanced classes possess distinct growth tables depending on their intermediate class route.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>readme_how_to_read</t>
+          <t>classes_title</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>## How to Read the Tables</t>
+          <t># Classes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Stat tables record raw class attributes at milestone levels from 1 to 99. Modifiers operate additively unless specified by game logic. Equipment usability lists weapon classes and defensive gear categories supported by internal compatibility bitmasks.</t>
+          <t>Progression tables, equipment access, weapon specialty modifiers, and skill trees for all 32 classes. Advanced classes with multiple prerequisite routes list independent growth tables for each path.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>readme_glossary</t>
+          <t>equip_section</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>## Glossary</t>
+          <t>#### Usable Equipment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Core combat parameters, calculations, and mechanical terms used throughout this guide.</t>
+          <t>Equipment compatibility based on class usability flags.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>classes_title</t>
+          <t>growth_section</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t># Classes</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Progression tables, equipment access, weapon specialty modifiers, and skill trees for all 32 classes. Advanced classes with multiple prerequisite routes list independent growth tables for each path.</t>
-        </is>
-      </c>
+          <t>#### Stat Growth</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>classes_intro</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>modifier_section</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>#### Weapon Specialty Modifiers</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Classes are organized into five base lines across three tiers: Base (Tier 1), Intermediate (Tier 2, Level 15), and Advanced (Tier 3, Level 30). Six Advanced classes possess distinct growth tables depending on their intermediate class route.</t>
+          <t>Equipping a specialized weapon, shield, or accessory grants a percentage bonus to all non-zero stats on that piece: `int((character_stat + piece_stat) * modifier)`.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>growth_section</t>
+          <t>overview_section</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>### Stat Growth</t>
+          <t>#### Class Overview</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -536,45 +533,66 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>equip_section</t>
+          <t>readme_glossary</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>### Usable Equipment</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>## Glossary</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Core combat parameters, calculations, and mechanical terms used throughout this guide.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>modifier_section</t>
+          <t>readme_how_to_read</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>### Weapon Specialty Modifiers</t>
+          <t>## How to Read the Tables</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Equipping a specialized weapon or gear type adds a percentage bonus: int((character_stat + piece_stat) * modifier) to all non-zero equipment stats (Address 0x4f7c60).</t>
+          <t>Stat tables record raw class attributes at milestone levels from 1 to 99. Modifiers operate additively unless specified by game logic. Equipment usability lists weapon classes and defensive gear categories supported by internal compatibility bitmasks.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>readme_title</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t># Dungeon Travelers 2-2 Reference Guide (Vanilla)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Player reference documentation for the original English PC release of Dungeon Travelers 2-2. All data, mechanics, and formulas are compiled directly from the original game files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>skills_section</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>### Learned Skills</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>#### Learned Skills</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -610,7 +628,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hit Points. Unit is incapacitated when reduced to 0.</t>
+          <t>Hit Points. The unit is knocked out when reduced to 0.</t>
         </is>
       </c>
     </row>
@@ -634,7 +652,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Attack stat (index 0). Scales physical damage before opponent DEF reduction (0x44b36e).</t>
+          <t>Physical attack power. Scales damage of normal attacks and physical skills before enemy DEF reduction.</t>
         </is>
       </c>
     </row>
@@ -646,7 +664,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Physical defence stat (index 1). Mitigates physical damage; subtracted from incoming attack values (0x44b9c0).</t>
+          <t>Physical defence. Reduces incoming physical damage directly from the attacker's attack value.</t>
         </is>
       </c>
     </row>
@@ -658,7 +676,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intelligence stat (index 2). Determines magic attack strength and magic evasion calculations (0x44dc97).</t>
+          <t>Intelligence. Determines magic attack power and influences magic evasion.</t>
         </is>
       </c>
     </row>
@@ -670,7 +688,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Resistance stat (index 3). Mitigates magic damage and provides base elemental protection (0x44e070).</t>
+          <t>Resistance. Reduces incoming magic damage and provides base protection against elemental attacks.</t>
         </is>
       </c>
     </row>
@@ -682,7 +700,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dexterity stat (index 4). Influences physical accuracy and critical hit chance (0x44aac1, 0x44f1d8).</t>
+          <t>Dexterity. Increases physical hit accuracy and critical hit chance.</t>
         </is>
       </c>
     </row>
@@ -694,7 +712,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Agility stat (index 5). Governs physical evasion and action gauge recovery rate (0x44aac1, 0x449b4c).</t>
+          <t>Agility. Increases physical evasion rate and speeds up action gauge recovery in the turn order.</t>
         </is>
       </c>
     </row>
@@ -706,7 +724,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Casting interval required by certain spells and skills before execution (0x449d9a). Damage taken relative to max HP creates interruption chance (0x44d001).</t>
+          <t>Casting preparation time required before executing certain spells and skills. Damage sustained relative to max HP can interrupt the chant.</t>
         </is>
       </c>
     </row>
@@ -718,7 +736,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Weapon recovery factor indexed by weapon rank (A+ to F). Increases turn wait time proportionally with unit level (0x449bd4).</t>
+          <t>Weapon recovery delay determined by weapon rank (A+ to F). Slower weapons increase the wait time before the unit's next turn, scaling with level.</t>
         </is>
       </c>
     </row>
@@ -730,7 +748,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Damage variance factor assigned to weapons, spells, and enemies (0x44b2f1, 0x44db97).</t>
+          <t>Inherent damage variance factor assigned to weapons, spells, and enemies.</t>
         </is>
       </c>
     </row>
@@ -742,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Accuracy versus evasion check. Physical hit rate is bounded between 5% and 100% (0x44ae84); spell hit rate is bounded between 25% and 95% (0x44da2b).</t>
+          <t>Accuracy check between attacker and target. Physical hit rate is bounded between 5% and 100%; offensive spells are bounded between 25% and 95%.</t>
         </is>
       </c>
     </row>
@@ -754,7 +772,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reduces damage of the corresponding attribute by 0.5% per point (0x44c576). Mitigates ailment infliction chance in increments of 10 points (0x481fc2).</t>
+          <t>Reduces damage of that element by 0.5% per point of resistance. Also mitigates status ailment infliction chance in increments of 10 points.</t>
         </is>
       </c>
     </row>
@@ -766,7 +784,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Position-based enmity value determining probability of being targeted by single-target attacks (0x43f7e9, table 0x6517a0).</t>
+          <t>Enmity value determining the likelihood of being targeted by single-target attacks, influenced by row position, Provoke, and equipment.</t>
         </is>
       </c>
     </row>
@@ -778,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Distance factor based on combat rows (front vs back). Melee skills lose damage over distance; ranged skills bypass distance penalties (0x44a7d0).</t>
+          <t>Distance between front and back combat rows. Short-range attacks lose damage when targeting or used from the back row; long-range attacks suffer no distance penalty.</t>
         </is>
       </c>
     </row>
@@ -790,7 +808,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Process of returning a character to level 1 from level 50 or higher (0x4f94f0). Grants permanent stat bonus points up to a hard cap of 50.</t>
+          <t>Returning a character to level 1 from level 50 or higher to earn permanent bonus stat points, up to a maximum of 50.</t>
         </is>
       </c>
     </row>
@@ -805,7 +823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -823,84 +841,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>agi</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>AGI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hp</t>
+          <t>atk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ATK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tp</t>
+          <t>bonus</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>Modifier</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>atk</t>
+          <t>category</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>Type</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>def</t>
+          <t>count</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>Count</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>def</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>DEF</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>res</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
@@ -919,192 +937,228 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>agi</t>
+          <t>equipment_type</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>Equipment Type</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>gear_categories</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Defensive Gear</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tier</t>
+          <t>hp</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tier</t>
+          <t>HP</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>int</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Promotion Route</t>
+          <t>INT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>weapon_types</t>
+          <t>level</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Weapon Types</t>
+          <t>Level</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gear_categories</t>
+          <t>line</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Defensive Gear</t>
+          <t>Line</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>slot</t>
+          <t>max_lv</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Slot</t>
+          <t>Max Lv</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>equipment_type</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Equipment Type</t>
+          <t>Class Overview</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bonus</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Modifier</t>
+          <t>Combat Role &amp; Profile</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>skill</t>
+          <t>range</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Range</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>res</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>RES</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>max_lv</t>
+          <t>route</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Max Lv</t>
+          <t>Promotion Route</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sp_cost</t>
+          <t>skill</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SP Cost</t>
+          <t>Skill</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>target</t>
+          <t>slot</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Slot</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>range</t>
+          <t>sp_cost</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>SP Cost</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>target</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Count</t>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>weapon_types</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Weapon Types</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1830,6 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1892,7 +1945,6 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2008,7 +2060,6 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2164,7 +2215,6 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2280,7 +2330,6 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2379,6 +2428,6793 @@
       <c r="D33" t="inlineStr">
         <is>
           <t>Trickster</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Class_ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fighter</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>With high physical strength and extraordinary stamina, these soldiers can wield a variety of short-range weapons. They act as vanguards who rout their foes whilst also shielding their comrades from attack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Paladin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Holy knights of the front line who protect their comrades by using themselves as human shields. They excel in defense and can handle skills which provide even more stability. Their purpose is to protect allies rather than defeat enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Berserker</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Short-range battle experts who excel at using two-handed swords and axes. They care little for weak attacks; instead, they obliterate enemies with a single powerful blow. An absolute must-have for an attack-focused party.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Valkyrie</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>They have no superior when it comes to short-range fortitude. With their immense strength and beauty, they are oft likened to war angels leading armies into battle. Their strong counterattack as they defend their allies seals the victory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Samurai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Swordswomen who inflict deadly slash damage with each swing. A single hit from one of their masterful skills can slice a foe in half. They also show great technical nous with their ability to dodge enemy strikes before mounting a swift counterattack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dark Lord</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Drawing power from the darkness, these battle goddesses will not stop until they have wholly consumed the lives and spirits of their opponents. The merciless blows delivered by these jet-black soldiers leave their enemies with nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Scout</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Using nimble body movements, they can create opportunities to not only attack, but also steal money. Their strength lies in how they can change battle styles depending on the situation, as they are skilled in both shortsword and bow techniques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Archer</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Archers, adept at providing support from long distances. They attack with great accuracy and can inflict various status ailments upon their targets. When faced with numerous adversaries, they can blacken the skies with a shower of arrows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Assassin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Shortsword users who employ agility to trick their foes, sneaking behind them to strike critical hits. Can both lead the attack and provide support by inflicting various status ailments. Their sharp strikes will occasionally dispatch an enemy in one hit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sniper</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>With their god-like speed, these long-range specialists pierce every target they set their eyes on. Their ultimate strikes are lethal to foes. Can use both warning shots and covering fire to provide support from a distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Treasure Hunter</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Able to wield a variety of weapons including shortswords, whips, and bows, as well as steal treasure from enemies. Using their trained judgement, they can also expertly manage and identify inventory. Treasurers who serve to enrich the party's wallet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kunoichi</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Spies who utilize their blazing speed to battle opponents. They use shadow clones to nullify enemy attacks, and sometimes fight with a sword in each hand. In addition to far-range shuriken strikes, they are also skilled in a multitude of martial arts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Magic User</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>A basic magician type who can use all general elements of magic. Their ability to replenish HP with Heal makes them a necessary member of any party.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sorceress</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Adept at magic attacks which cover a wide area. Their low defense can be a problem, but they provide stellar support with extraordinarily powerful magic. Capable of either dabbling in multiple elements or mastering one in particular.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Enchantress</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Technical masters who can imbue allies' weapons with various elemental abilities. This skill can be difficult to properly manage, especially when taking into account varying enemy weaknesses. Their true worth is in the excellent support they provide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Priestess</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>A rear support class that specializes in healing magic. They can heal the party, revive fallen comrades, and use a wide-reaching, albeit single-element, magic attack. There can be no doubt regarding their importance in lengthy dungeon explorations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Witch</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Attack experts, able to cast the most powerful spells of each elemental set. Top-rank area attacks wipe out enemy parties, whilst destructive solo attacks obliterate single enemies, leaving not even a trace of their meager existence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Magical Princess</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Magical girls who can handle even hand-to-hand combat with love and vigor. After using Magical Change to heighten their abilities, they clean up their foes with area attacks. Per their name, they also wield magic, making them great all-around fighters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sage</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>A support class specializing in magic that provides buffs to their allies. Possessing skills which automatically heal status ailments, they display their true power in lengthy encounters. They can swing the inevitable tough battles in your favor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bishop</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Healing gurus in control of powerful restorative magic, such as party-wide healing of status ailments. They are formidable in attack as well, with mighty skills like Holy Gavel or Justice. Bishops greatly increase the survival rate of their party.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Maid</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Skilled at neither physical attack nor magic, but can activate a wide range of special effects in battle without needing to chant beforehand or expend TP. They tend to fill the role of the unsung hero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bard</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Singers whose stunning voices strengthen the entire party. Since their battle capabilities are limited, they primarily reside in the back row where their allies can defend them. Their songs motivate, heal, and overall act as a huge support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dancer</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>A technical class that is primarily responsible for debuffing their adversaries. Members of this class captivate their enemies by performing a whole-body dance routine. Those who observe their dazzling techniques become weakened and cursed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Diva</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Support class specializing in skills that boost the abilities of their comrades. With vocals that could rattle even the Milky Way, they provide courage to all who listen and send off their comrades in a much improved state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mistress</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Hard workers who finally reached the status of master after extensive work as subordinate maids. As if affected by past trauma, they tend to exhibit quite sadistic behavior. Their favorite weapon is the whip, and they love to castigate their rivals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Etoile</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Admired by all as they soar across the battlefield. Even enemies are captivated by their ravishing dances. Not only are they delightfully dainty, but they are known to rescue their comrades from danger, even at the cost of their own lives!</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Spieler</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>An eccentric class with many skills, the effects of which are left completely up to chance. It is an utter mystery whether or not they are actually useful...</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Doll Master</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>By breathing life into puppets, members of this class are able to create their own underlings. Since the puppets take on lives of their own and act without any direct input from their masters, the summoner herself is able to maneuver freely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Trickster</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Rather than consistency, members of this class relish the instability that comes with not knowing what will happen. In times of great danger, they may be able to turn the tables in your party's favor... Maybe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Soul Summoner</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>The highest rank of puppeteer, this class can employ immensely powerful puppets. They possess skills such as the ability to breathe life into two puppets at once or to absorb the power of the equipped Sealbook and bestow it upon their servants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Papillon</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Using hand-fans proficiently as weapons, they are skilled in both short and long distance combat. They are unique not only in weapon choice, but also skill selection, most notable of which is an ultimate skill that turns a weakened enemy into... food?</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Joker</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Death gods who wander the battlefield in search of enemy blood. However, they quickly tire of this hunt, so instead drink their own blood in order to transform into a destroyer. This haunting visage strikes fear into the hearts of all onlookers.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D313"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Skill_ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Provoke</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Attract an enemy's attacks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Attract</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Attract all enemies' attacks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>War Cry</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Raise the party's ATK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Raging Smash</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Short-range skill. Powerful strike to one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Aura Eliminate</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Short-range skill. Attack one enemy. May cancel enemy buffs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Berserk</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Increase own ATK at the price of lowering own DEF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Defender</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Increase own DEF at the price of lowering own ATK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Shield Bash</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Shield skill. Deal bash damage to one enemy. May stun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Backward Swing</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Katana skill. Deal bash damage to one enemy. May paralyze.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Last Stand</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Raise own critical rate, but also own vulnerability to critical hits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Halving Slice</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Katana skill. Deal slash damage to an enemy row. May instakill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Armor Penetration</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Katana skill. Deal defense-piercing damage and DEF down to one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Onikagura</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Katana skill. Deal slash damage to an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Moonlight Purgatory</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Katana skill. Deal slash damage 3 times to one enemy. Living targets only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Blood Drain</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Short-range skill. Attack one enemy to regain HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Soul Drain</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Short-range skill. Attack one enemy to regain TP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Frost Slash</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Short-range skill. Deal mid-range water damage to one enemy. May freeze.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Geo Break</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Axe skill. Deal earth damage to one enemy. May petrify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Megaton Press</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Axe skill. Attack an enemy, then the next immediate enemy in the turn order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Take all physical damage in place of one ally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Parry</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Short-range skill. Use one's weapon to repel enemy attacks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Cross Slash</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sword/lance skill. Attack one enemy (effective vs. unholy monsters).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Material Guard</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Shield skill. Reduce physical damage taken by the party once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Spell Guard</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Shield skill. Reduce magic damage taken by the party once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Shock Spiral</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Short-range skill. Deal lightning damage to an enemy row. May paralyze.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Gust Thrust</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Lance skill. Deal wind damage to one enemy. May silence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Daedalus Attack</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Lance skill. 3-5 hits on random enemies. Stronger with a Heavy Lance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ether Strike</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sword/lance skill. Pierces through to the back row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Power Charge</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Deal increased physical damage next turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Gold Steal</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Steal pocket money from an enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Item Steal</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Steal an item from an enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sharp Stab</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Dagger skill. Inflict a critical hit with stab damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Pursuit Stab</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Dagger skill. Inflict stab damage relative to enemy's total buffs and debuffs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Evade</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Increase own physical evasion rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Cleanse</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Cure status ailments for a single ally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Aim</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Increase own accuracy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Fleet Foot</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Increase own speed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Warm-Up</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Increase own physical evasion rate and magical evasion rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sleep Sting</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Short-range skill. Attack one enemy. May cause sleep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>39</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Silence Sting</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Short-range skill. Attack one enemy. May silence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>40</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Stun Sting</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Short-range skill. Attack one enemy. May stun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>41</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Chain Spike</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Bow/gun skill. Attack one enemy multiple times with escalating crit rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>42</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Guided Shot</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Bow/gun skill. Fire a single shot certain to hit one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>43</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Spiral Arrow</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Bow skill. Shoot a powerful single shot at one enemy for stab damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>44</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Poison Shot</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Bow/gun skill. Attack one enemy. May poison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>45</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Freeze Shot</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Bow skill. Deal stab damage to one enemy. May freeze.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>46</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Paralysis Shot</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Bow skill. Deal stab damage to one enemy. May paralyze.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>47</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Gravity Shot</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Bow skill. Deal stab damage to one enemy. May slow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>48</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Arrow Rain</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Bow skill. Shoot a barrage of arrows that rains upon all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>49</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Star Dust Arrow</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bow skill. Shower enemies with a rain of arrows across multiple turns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>50</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Divine Cannon</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Bow skill. Deal stab damage to one enemy and pierce to the back row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>51</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Projectile skill. Attack and decrease speed for an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>52</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ninja Piledriver</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Deal bash damage to one enemy. May stun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>53</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Identify unknown items.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>54</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Loose Spirit</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Briefly sacrifice magic accuracy to increase magic damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>55</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Holy Gavel</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Mace skill. Deal bash damage with an inexorable thud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>56</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Justice</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Mace skill. Decrease the enemy's DEF as you attack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>57</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Magical Slash</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Sword skill. Deal slash damage to all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>58</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Magic Barrier</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Reduce magic damage taken for the party.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>59</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Magical Change</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Transform to increase own overall stats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>60</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Magical Spark</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Short-range skill. Perform a powerful lightning strike to one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>61</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Bible Thump</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Tome skill. RES-based bash damage to one enemy. May freeze/silence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>62</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Trap Search</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Protect allies from gas and damage traps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>63</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Treasure Search</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Detect how many unopened treasure chests are left on the current floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>64</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>First Aid</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Heal an ally's HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>65</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Cook</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Heal an ally's TP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>66</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Self-Sacrifice</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Distribute all of one's TP to the target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>67</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Clean</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Clean one's surroundings in order to increase mobility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>68</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Holy Prayer</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Recover some TP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>69</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Fascinating Waltz</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Dance skill. Lower all enemies' ATK while dance lasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>70</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Alluring Samba</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Dance skill. Lower all enemies' DEF while dance lasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>71</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Gloomy Tango</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Dance skill. Lower all enemies' accuracy while dance lasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>72</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Gravitating Polka</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Dance skill. Lower all enemies' evasion while dance lasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>73</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Debilitating Salsa</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Dance skill. Damage all enemies at the start of user's turn while dance lasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>74</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Dumbing Mazurka</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Dance skill. Lower all enemies' speed while dance lasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>75</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Emaciating Hopak</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Dance skill. Lower all enemies' elemental resistances while dance lasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>76</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Hard Whipping</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Whip skill. Deal bash damage to an enemy row from mid-range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>77</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Enticing Love</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Whip skill. Attack one enemy 1-5 times from mid-range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>78</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Absolute Obedience</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Whip skill. Deal bash damage to one enemy twice. May silence/paralyze.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>79</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Danger Shoot</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Attack 0-4 times on random targets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>80</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Coffee Break</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Take a break to heal own HP and raise Pep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>81</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Roulette Circus</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Spin the magic roulette. Nobody knows what will happen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>82</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Checkmate</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Attack one enemy. May instakill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>83</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Surprise Fist</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>50/50 chance of non-elemental damage to each enemy. May stun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>84</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>High Risk, High Return</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Increase own ATK at the price of lowering own DEF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>85</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Magic Box</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Open a magic box. Nobody knows what will happen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>86</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Materialize</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Turn a weakened enemy into food. Ineffective against some enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>87</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Rose Queen</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Deal non-elemental damage to all enemies with a storm of roses. May poison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>88</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Tinker Squash</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Fan skill. Deal bashing damage to one enemy. May delay enemy turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>89</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Graceful Rose</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Fan skill. With increased ATK, deal long-range damage to one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>90</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Mad Zapper</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Short-range skill. Pierce through to the back row with stab damage. May slow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>91</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Life Bringer</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Short-range skill. Attack one enemy and reduce target's max HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>92</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Trump Card</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Convert current DEF to bonus ATK (DEF becomes 0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>93</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Showtime</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Something emerges from the shadows. Nobody knows what will happen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>94</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Beast Binder</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Whip skill. Attack one enemy 1-3 times from mid-range. Crits against Beasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>95</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Spartan</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Summon Spartan for short-range bash damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>96</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Oracles</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Summon Oracles for mid-range INT-based damage and possible paralysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>97</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Catalina</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Summon Catalina to heal allies' HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>98</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Mercidarian</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Summon Mercidarian for random long-range stab damage to all foes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>99</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Perdurabo</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Summon Perdurabo to cure two allies' status ailments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>100</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Musiy</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Summon Musiy for immediate single-target attack magic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>101</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Spartan's Action</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Actual course of action</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>102</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Oracles' Action</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Actual course of action</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>103</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Mercidarian's Action</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Actual course of action</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>104</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Catalina's Action</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Actual course of action</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>105</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Perdurabo's Action</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Actual course of action</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>106</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Star Dust Arrow's Action</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Actual course of action</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>107</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Genjimaru's Action</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Actual course of action</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>108</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Roulette Circus Effect</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Poison all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>109</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Roulette Circus Effect</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Freeze all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>110</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Roulette Circus Effect</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Paralyze all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>111</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Roulette Circus Effect</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Silence all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>112</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Roulette Circus Effect</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Slow all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>113</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Roulette Circus Effect</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Heal one random ally for 20% of HP and TP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>114</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Roulette Circus Effect</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Fully heal one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>115</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Roulette Circus Effect</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Deal own level x10 damage to one random ally or enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>116</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Roulette Circus Effect</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Nothing happens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>117</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Magic Box Effect</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Deal damage equal to own remaining HP - 1 to one random ally or enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>118</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Magic Box Effect</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>A long-range + stab attack to all enemies. Inflicted damage is based off the practitioner's ATK</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>119</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Magic Box Effect</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Song, dance, doll, and chant are canceled for all enemies and allies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>120</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Magic Box Effect</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Recover 75TP for the party.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>121</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Magic Box Effect</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>An unknown dog (Genjimaru) appeared for support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>122</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Magic Box Effect</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Attack oneself with own ATK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>123</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Magic Box Effect</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Acquire the total amount of money for beating all enemies there x4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>124</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Magic Box Effect</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Inflict a fixed damage of 666 to someone from your enemies or allies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>125</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Magic Box Effect</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Nothing happens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>126</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Magic Box Effect</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Instant death for the practitioner</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>127</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Magic Box Effect</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Recover 200HP for the party.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>128</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Showtime Effect</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Circle Brave and Circle Protect activated for an ally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>129</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Showtime Effect</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Fully recover HP for the one with the highest rate of TP loss out of your allies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>130</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Showtime Effect</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Stab, Cut, and Bash Protect Lv5 activated for the party.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>131</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Showtime Effect</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Stun the party.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>132</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Showtime Effect</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Put the party to sleep. (Guaranteed without perfect sleep resistance.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>133</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Showtime Effect</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Silence + freeze + slow for all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>134</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Showtime Effect</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>HP gets cut down to half for the party.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>135</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Showtime Effect</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Aim and Fleet Foot Lv10 activated for the party.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>136</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Showtime Effect</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>HP and TP fully recovered for all enemies and allies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>137</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Showtime Effect</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Enemies will flee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>138</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Showtime Effect</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Scatter 1/10 of pocket money your ally has.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>139</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Showtime Effect</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Attack an enemy 7 times with own ATK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>140</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Showtime Effect</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Nothing happens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>141</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Heaven or Hell Effect</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Damage one enemy for a percentage of HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>142</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Heaven or Hell Effect</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Heal one enemy for a percentage of HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>143</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Fireball</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Deal fire damage to one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>144</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Fire Blast</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Deal fire damage to an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>145</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Inferno</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Deal fire damage to all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>146</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Crimson Flare</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Deal tremendous fire damage to one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>147</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Ice Edge</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Deal water damage to one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>148</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Ice Storm</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Deal water damage to an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>149</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Diamond Dust</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Deal water damage to all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>150</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Cocytus</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Deal tremendous water damage to one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>151</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Thunderbolt</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Deal lightning damage to one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>152</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Thunder Chain</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Deal lightning damage to an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>153</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Deal lightning damage to all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>154</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Muon Plasma</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Deal tremendous lightning damage to one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>155</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Air Cutter</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Deal wind damage to one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>156</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Air Turbulence</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Deal wind damage to an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>157</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Tornado</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Deal wind damage to all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>158</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Tempest</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Deal tremendous wind damage to one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>159</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Stone Hammer</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Deal earth damage to one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>160</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Stone Shower</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Deal earth damage to an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>161</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Meteor</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Deal earth damage to all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>162</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Gaia Crush</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Deal tremendous earth damage to one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>163</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Blood Absorb</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Deal non-elemental damage to one enemy to regain HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>164</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Soul Absorb</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Deal non-elemental damage to one enemy to regain TP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>165</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Blood Rage</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Raise max HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>166</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Life Bring</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Absorb HP from an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>167</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Stun</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Stun one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>168</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Poison</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Poison all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>169</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Freeze</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Freeze all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>170</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Paralyze</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Paralyze all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>171</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Put an enemy row to sleep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>172</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Silence</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Silence all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>173</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Petrify</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Petrify an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>174</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Death</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Instakill one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>175</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Slow</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Slow an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>176</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Terrorize</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Stun an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>177</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Dispel</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Negate buffs for all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>178</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Shine Curse</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Deal non-elemental damage to all enemies (effective vs. unholy monsters).</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>179</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Fire Enchant</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Imbue an ally's weapon with fire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>180</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Water Enchant</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Imbue an ally's weapon with water.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>181</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Lightning Enchant</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Imbue an ally's weapon with lightning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>182</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Wind Enchant</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Imbue an ally's weapon with wind.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>183</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Earth Enchant</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Imbue an ally's weapon with earth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>184</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Stab Guard</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Raise one row of allies' resistance to stab damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>185</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Slash Guard</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Raise one row of allies' resistance to slash damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>186</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Bash Guard</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Raise one row of allies' resistance to bash damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>187</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Heal an ally's HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>188</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Circle Heal</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Heal the party's HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>189</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Full Heal</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Fully heal one ally's HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>190</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Nurse</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Cure status ailments for a single ally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>191</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Circle Nurse</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Cure party's status ailments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>192</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Resurrect</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Revive a dead ally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>193</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Brave</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Raise an ally's ATK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>194</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Raise an ally's DEF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>195</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Sun Veil</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Raise the party's magic defense.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>196</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Moon Curtain</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Raise the party's resistance to fire, water, lightning, wind, and earth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>197</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Accelerator</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Raise an ally's speed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>198</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Raise an ally's max HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>199</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Mini Circle Nurse</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Cure one row of allies' status ailments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>200</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Illusion</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Create 2 magical afterimages that let you dodge one attack each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>201</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Divine Shield</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Reduce incoming physical damage by a certain amount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>202</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>While active, immediately revive upon death.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>203</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Illuminate the dungeon to find hidden pathways.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>204</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Return</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Escape from the dungeon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>205</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Lullaby</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Put an enemy to sleep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>206</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Barrage Rondo</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Raise the party's chance of doing multiple strikes while song lasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>207</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Concentration Prelude</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Raise the party's critical rate while song lasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>208</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Spiritual Fantasia</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Raise the party's magic attack power while song lasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>209</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Sacred Hymn</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Raise the party's magic defense power while song lasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>210</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Reading Requiem</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Decrease the party's chant time while song lasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>211</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Replenishing Carol</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Gradually heal the party's HP while song lasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>212</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Blissful Chorale</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Gradually heal the party's TP while song lasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>213</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Lightning March</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Raise the party's speed while song lasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>214</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Experience Paean</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Raise the party's acquired EXP while song lasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>215</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Sorcerous Ballad</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Raise the party's magic accuracy while song lasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>216</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Shadow Clone</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Dodge enemy attacks by creating a shadow clone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>217</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Shadow Sew</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Disable skill usage for an enemy row. Level must exceed the target's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>218</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Light Scroll</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Lower all enemies' accuracy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>219</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Fire Scroll</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Deal fire damage based on enemy's max HP and lower ATK to an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>220</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Water Scroll</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Deal water damage based on enemy's max HP and lower magic def. to an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>221</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Lightning Scroll</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Deal lightning damage based on enemy's max HP and lower speed to an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>222</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Wind Scroll</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Deal wind damage based on enemy's max HP and lower evasion to an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>223</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Earth Scroll</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Deal earth damage based on enemy's max HP and lower DEF to an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>224</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Rainbow Flash</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Deal non-elemental damage to an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>225</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Panic Voice</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Deal non-elemental damage to all enemies. May stun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>226</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Circle Brave</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Raise the party's ATK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>227</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Circle Protect</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Raise the party's DEF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>228</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Limit Field</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Create a field that reduces damage for both sides for a time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>229</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Raise encounter rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>230</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Primevil</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Sacrifice yourself to revive, heal, and recover status effects for the rest of the party.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>231</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Carrot and Stick</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Heal an enemy's HP to decrease its physical and magic defense.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>232</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Prism Dawn</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Pierce to the back row with a raw magic attack and RES-based extra damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>233</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Soul Eater</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Deal enormous damage to one enemy that possesses life. Low chance of instakill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>234</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Heaven or Hell</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Either heal or damage an enemy based on the enemy's HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>235</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Musiy's Action (Fireball)</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Actual course of action</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>236</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Musiy's Action (Ice Edge)</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Actual course of action</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>237</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Musiy's Action (Thunderbolt)</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Actual course of action</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>238</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Musiy's Action (Air Cutter)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Actual course of action</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>239</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Musiy's Action (Stone Hammer)</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Actual course of action</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>240</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Arcane Shield</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Deal direct damage back to attacker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>241</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Sword Mastery</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>ATK bonus with sword equipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>242</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Axe Mastery</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>ATK bonus with axe equipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>243</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Dagger Mastery</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>ATK bonus with dagger equipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>244</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Mace Mastery</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>ATK bonus with mace equipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>245</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Lance Mastery</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>ATK bonus with lance equipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>246</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Bow Mastery</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>ATK bonus with bow equipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>247</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Katana Mastery</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>ATK bonus with katana equipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>248</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Projectile Mastery</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>ATK bonus with projectile weapon equipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>249</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Whip Mastery</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>ATK bonus with whip equipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>250</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Fan Mastery</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>ATK bonus with fan equipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>251</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Weapon Mastery</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>ATK bonus for all weapons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>252</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Magic Mastery</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Magic attack power bonus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>253</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Heal Mastery</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Healing magic bonus. Raises healing cap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>254</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Auto-Recovery</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Recover HP every turn during battle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>255</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Mini Auto-Recovery</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Slightly recover HP every turn during battle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>256</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Auto-Refresh</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Recover TP every turn during battle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>257</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Mini Auto-Refresh</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Slightly recover TP every turn during battle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>258</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Adaptation</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Raise resistance to all elements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>259</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Avenger</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Occasionally counterattack after receiving physical damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>260</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Mind's Eye</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Occasionally parry and counterattack when targeted by an enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>261</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Double Attack</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Occasionally attack twice when attacking normally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>262</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Triple Attack</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Occasionally attack thrice when attacking normally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>263</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Flowing Water Stance</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Increase evasion rate against stab attacks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>264</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Knock Down</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Occasionally parry when receiving long-range attacks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>265</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Guts</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Occasionally survive at 1 HP after being dealt fatal damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>266</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Auto-Guard</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Occasionally Defend automatically when receiving physical attacks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>267</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Dual Wield</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Can equip two one-handed weapons at the same time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>268</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Grudge Accumulator</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Convert some received damage to TP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>269</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Murder</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Occasionally instakill when inflicting a critical hit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>270</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Warning Shot</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>With bow equipped, occasionally halt an enemy's action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>271</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Support Shot</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>With bow equipped, occasionally attack again after an ally's attack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>272</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Preparation</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Gain increased speed based on missing HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>273</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Dark Aura</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Debuff an enemy when they inflict short-range damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>274</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Dark Quest</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Increase ATK while inflicted with status ailments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>275</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Anti-Dark Aura</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Nullify the effects of enemy Dark Auras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>276</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Absolute Attack</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>No longer suffer counterattacks from enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>277</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Imperial Guard</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Decrease physical damage to the back row when using a shield in the front row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>278</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Pretend</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Occasionally nullify physical damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>279</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Esarhaddon</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Automatically heal inflicted status ailments at the start of each turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>280</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Ecstasy</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Briefly increase ATK and DEX when HP drops below 50%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>281</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Concentrate</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Make it harder for chants, songs, and dances to be interrupted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>282</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Fast Cast</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Reduce chant time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>283</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Reduce TP Cost in battle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>284</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Nirvana</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Heighten magic accuracy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>285</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Limit enemies' preemptive attacks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>286</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Increase party's preemptive attack rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>287</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Elusiveness</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>May escape from battle more easily.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>288</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Treasure Hunt</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Increase the enemies' item drop rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>289</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Lucky Me</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Increase the amount of money the enemies drop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>290</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Present for Me</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Sometimes pick up items while moving around the dungeons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>291</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Generous Heart</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Party's HP and TP is restored slightly after a battle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>292</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Recycle</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Occasionally keep disposable items after using them in battle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>293</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Item Mastery</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Increase the effects of HP and TP recovery items during battle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>294</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Self Session</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Become capable of performing two songs at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>295</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>On Stage</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Become capable of performing two dances at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>296</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Double Puppet</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Become capable of controlling two dolls at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>297</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Soul Seal</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Increase doll power with the strength of the equipped Sealbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>298</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Maid Mastery</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Increased effects for all maid skills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>299</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Song Mastery</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Increased effects for all songs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>300</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Dance Mastery</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Increased effects for all dances.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>301</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Doll Mastery</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Increased effects for all doll skills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>302</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Barrage</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Occasionally attack twice when attacking normally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>303</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Fast Talk</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Reduce chant time for songs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>304</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Negotiate</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Reduce purchase and identification prices at shops.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>305</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Magnificent Steps</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Mesmerize enemies, causing them to occasionally do nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>306</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Elegant Dancing</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Nullify first hit of battle against user (does not work for status ailments).</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>307</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Triple Joker</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Heighten the probability of beneficial results for random effect skills.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>308</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Counter Whip</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Whip skill. Strike back with a normal attack before a targeted attack hits you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>309</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>First Grid</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Occasionally get the first action regardless of speed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>310</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Critical Magic</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Occasionally land critical hits with offensive spells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>311</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Destiny Line</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Increase doll summon duration by 1 turn.</t>
         </is>
       </c>
     </row>

--- a/data_tables/guide_text.xlsx
+++ b/data_tables/guide_text.xlsx
@@ -498,7 +498,6 @@
           <t>#### Stat Growth</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -528,7 +527,6 @@
           <t>#### Class Overview</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -592,7 +590,6 @@
           <t>#### Learned Skills</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -918,7 +915,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Effect &amp; Scaling</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1107,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SP Cost</t>
+          <t>Total SP</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D313"/>
+  <dimension ref="A1:E313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2977,6 +2974,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Scaling</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2997,6 +2999,12 @@
           <t>Attract an enemy's attacks.</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Enmity: 250
+Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5   |   Speed: 1.5x -&gt; 2x</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3017,6 +3025,12 @@
           <t>Attract all enemies' attacks.</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Enmity: 150
+Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 | TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 | Speed: 1.25x -&gt; 1.77x</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3037,6 +3051,12 @@
           <t>Raise the party's ATK.</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ATK: +8% -&gt; +10% -&gt; +12% -&gt; +15% -&gt; +18% (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 5 -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3057,6 +3077,12 @@
           <t>Short-range skill. Powerful strike to one enemy.</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ATK: 125% -&gt; 134 -&gt; 143 -&gt; 152 -&gt; 161 -&gt; 170 -&gt; 178 -&gt; 186 -&gt; 193 -&gt; 200% (L10)
+Accuracy: +20% (+2%/Lv)   |   TP Cost: 5 (+2-3/Lv) -&gt; 28   |   Speed: 0.8x -&gt; 0.9x</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3077,6 +3103,12 @@
           <t>Short-range skill. Attack one enemy. May cancel enemy buffs.</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Accuracy: +20% -&gt; +22 -&gt; +24 -&gt; +26 -&gt; +28 -&gt; +30 -&gt; +31 -&gt; +32 -&gt; +33 -&gt; +35% (L10)
+Buff cancel rate: 68% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 5 (+1-2/Lv) -&gt; 18   |   Speed: 0.9x</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3097,6 +3129,12 @@
           <t>Increase own ATK at the price of lowering own DEF.</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ATK: +20% -&gt; +30% -&gt; +40% -&gt; +45% -&gt; +50% (L1-5 Max)
+DEF: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25%   |   Turns: 4 -&gt; 8   |   TP Cost: 8 (+2/Lv) -&gt; 16</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3117,6 +3155,12 @@
           <t>Increase own DEF at the price of lowering own ATK.</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DEF: +20% -&gt; +30% -&gt; +40% -&gt; +45% -&gt; +50% (L1-5 Max)
+ATK: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25%   |   Turns: 4 -&gt; 8   |   TP Cost: 8 (+2/Lv) -&gt; 16</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3137,6 +3181,12 @@
           <t>Shield skill. Deal bash damage to one enemy. May stun.</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ATK: 85% -&gt; 90% -&gt; 94% -&gt; 98% -&gt; 102% (L1-5 Max)   |   Accuracy: +6% (+3-4%/Lv) -&gt; +20%
+Stun: 30% -&gt; 32% -&gt; 34% -&gt; 36% -&gt; 38%   |   TP Cost: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3157,6 +3207,12 @@
           <t>Katana skill. Deal bash damage to one enemy. May paralyze.</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ATK: 106% -&gt; 112 -&gt; 118 -&gt; 124 -&gt; 130 -&gt; 134 -&gt; 138 -&gt; 142 -&gt; 146 -&gt; 150% (L10)
+Accuracy: +5% (+2-3%/Lv) -&gt; +28%   |   Paralysis: 20% -&gt; 50%   |   TP Cost: 6 (+2/Lv) -&gt; 24</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3177,6 +3233,12 @@
           <t>Raise own critical rate, but also own vulnerability to critical hits.</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Critical rate: 5% (+2.5%/Lv) -&gt; 15% (L5 Max)   |   Enemy critical rate: 4% (+2%/Lv)
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3197,6 +3259,12 @@
           <t>Katana skill. Deal slash damage to an enemy row. May instakill.</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ATK: 80% -&gt; 83 -&gt; 86 -&gt; 89 -&gt; 91 -&gt; 94 -&gt; 97 -&gt; 100 -&gt; 105 -&gt; 110% (L10)
+Instakill: 10% (+1-2%/Lv) -&gt; 20%   |   Power decrease: 10%   |   TP Cost: 38 (+4/Lv) -&gt; 74</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3217,6 +3285,12 @@
           <t>Katana skill. Deal defense-piercing damage and DEF down to one enemy.</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ATK: 84% -&gt; 88 -&gt; 92 -&gt; 96 -&gt; 100 -&gt; 104 -&gt; 108 -&gt; 112 -&gt; 116 -&gt; 120% (L10)
+Enemy DEF: -16% (-1%/Lv)   |   Turns: 4   |   TP Cost: 14 (+2/Lv) -&gt; 32   |   Speed: 0.8x</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3237,6 +3311,12 @@
           <t>Katana skill. Deal slash damage to an enemy row.</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ATK: 104% -&gt; 108 -&gt; 112 -&gt; 116 -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140% (L10)
+TP Cost: 22 -&gt; 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 54 -&gt; 58</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3257,6 +3337,12 @@
           <t>Katana skill. Deal slash damage 3 times to one enemy. Living targets only.</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ATK: 118% -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 146 -&gt; 152 -&gt; 158% (L10)
+Critical rate: 10%   |   TP Cost: 36 (+2-3/Lv) -&gt; 61   |   Speed: 0.7x -&gt; 0.8x</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3277,6 +3363,12 @@
           <t>Short-range skill. Attack one enemy to regain HP.</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ATK: 74% (+4%/Lv) -&gt; 110% (L10 Max)   |   HP Absorb: 15% (+1-2%/Lv) -&gt; 25%
+TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36   |   Speed: 0.9x</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3297,6 +3389,12 @@
           <t>Short-range skill. Attack one enemy to regain TP.</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ATK: 65% -&gt; 70 -&gt; 75 -&gt; 80 -&gt; 84 -&gt; 88 -&gt; 91 -&gt; 94 -&gt; 97 -&gt; 100% (L10)
+TP Absorb: 10% (+1-2%/Lv) -&gt; 20%   |   TP Cost: 6 (+2/Lv) -&gt; 24   |   Speed: 0.9x</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3317,6 +3415,12 @@
           <t>Short-range skill. Deal mid-range water damage to one enemy. May freeze.</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ATK: 130% -&gt; 144 -&gt; 157 -&gt; 170 -&gt; 182 -&gt; 194 -&gt; 204 -&gt; 212 -&gt; 220 -&gt; 228% (L10)
+Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   Accuracy: +14%   |   TP Cost: 9 (+3/Lv) -&gt; 36</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3337,6 +3441,12 @@
           <t>Axe skill. Deal earth damage to one enemy. May petrify.</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ATK: 135% (+11-14%/Lv) -&gt; 247%   |   Petrify: 20% (+1-2%/Lv) -&gt; 35%   |   Accuracy: +10%
+TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 37 -&gt; 42</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3357,6 +3467,12 @@
           <t>Axe skill. Attack an enemy, then the next immediate enemy in the turn order.</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ATK: 120% -&gt; 130 -&gt; 140 -&gt; 148 -&gt; 156 -&gt; 164 -&gt; 170 -&gt; 176 -&gt; 180 -&gt; 184% (L10)
+Targets: 2 (Lv1-3) -&gt; 3 (Lv4-6) -&gt; 4 (Lv7-8) -&gt; 5 (L9-10)   |   TP: 26 (+4-6/Lv) -&gt; 68</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3377,6 +3493,12 @@
           <t>Take all physical damage in place of one ally.</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Cover ends per hit: 70% -&gt; 62% -&gt; 54% -&gt; 46% -&gt; 40% (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 10 -&gt; 14 -&gt; 18 -&gt; 21 -&gt; 24</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3397,6 +3519,12 @@
           <t>Short-range skill. Use one's weapon to repel enemy attacks.</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Parry ends per block: 80% -&gt; 72% -&gt; 64% -&gt; 58% -&gt; 52% (L1-5 Max)
+Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3417,6 +3545,12 @@
           <t>Sword/lance skill. Attack one enemy (effective vs. unholy monsters).</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ATK: 130% -&gt; 140 -&gt; 150 -&gt; 160 -&gt; 170 -&gt; 180 -&gt; 190 -&gt; 200 -&gt; 211 -&gt; 222% (L10)
+Accuracy: +6% -&gt; +20%   |   Damage vs. unholy: +65%   |   TP Cost: 12 (+3/Lv) -&gt; 39</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3437,6 +3571,12 @@
           <t>Shield skill. Reduce physical damage taken by the party once.</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Damage reduction rate: 12% -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30%
+Turns: 5   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3457,6 +3597,12 @@
           <t>Shield skill. Reduce magic damage taken by the party once.</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Damage reduction rate: 12% -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30%
+Turns: 5   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40 -&gt; 43 -&gt; 45</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3477,6 +3623,12 @@
           <t>Short-range skill. Deal lightning damage to an enemy row. May paralyze.</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ATK: 96% -&gt; 100 -&gt; 104 -&gt; 108 -&gt; 113 -&gt; 118 -&gt; 123 -&gt; 128 -&gt; 133 -&gt; 138% (L10)
+Paralysis: 20% (+2-3%/Lv) -&gt; 40%   |   TP Cost: 26 (+4-5/Lv) -&gt; 64   |   Speed: 0.8x</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3497,6 +3649,12 @@
           <t>Lance skill. Deal wind damage to one enemy. May silence.</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ATK: 135% -&gt; 149 -&gt; 163 -&gt; 176 -&gt; 189 -&gt; 201 -&gt; 213 -&gt; 223 -&gt; 234 -&gt; 245% (L10)
+Silence: 20% (+3-4%/Lv) -&gt; 50%   |   Accuracy: +15%   |   TP Cost: 7 (+3/Lv) -&gt; 34</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3517,6 +3675,12 @@
           <t>Lance skill. 3-5 hits on random enemies. Stronger with a Heavy Lance.</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ATK: 116% -&gt; 118 -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 146 -&gt; 152% (L10)
+Heavy Lance bonus: +20%   |   TP Cost: 36 (+3-6/Lv) -&gt; 71   |   Speed: 0.7x -&gt; 0.8x</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3537,6 +3701,12 @@
           <t>Sword/lance skill. Pierces through to the back row.</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ATK: 120% -&gt; 130 -&gt; 142 -&gt; 154 -&gt; 165 -&gt; 176 -&gt; 186 -&gt; 196 -&gt; 204 -&gt; 212% (L10)
+Accuracy: +5% (+1-2%/Lv) -&gt; +15%   |   TP Cost: 32 (+3/Lv) -&gt; 59   |   Speed: 0.8x</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3557,6 +3727,12 @@
           <t>Deal increased physical damage next turn.</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Damage: 2.05x -&gt; 2.1x -&gt; 2.16x -&gt; 2.22x -&gt; 2.3x (L1-5 Max)
+Turns: 2   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Speed: 0.84x -&gt; 0.9x</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3577,6 +3753,12 @@
           <t>Steal pocket money from an enemy.</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Steal success: 40% -&gt; 45% -&gt; 50% -&gt; 57% -&gt; 64% (L1-5 Max)
+Speed: 1x -&gt; 1.5x</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3597,6 +3779,12 @@
           <t>Steal an item from an enemy.</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Steal success: 30% -&gt; 35% -&gt; 40% -&gt; 45% -&gt; 50% (L1-5 Max)
+Speed: 0.6x -&gt; 0.8x</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3617,6 +3805,12 @@
           <t>Dagger skill. Inflict a critical hit with stab damage.</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ATK: 105% -&gt; 109 -&gt; 113 -&gt; 116 -&gt; 119 -&gt; 121 -&gt; 123 -&gt; 125 -&gt; 127 -&gt; 129% (L10)
+TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26 -&gt; 28 -&gt; 30   |   Speed: 0.9x</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3637,6 +3831,12 @@
           <t>Dagger skill. Inflict stab damage relative to enemy's total buffs and debuffs.</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ATK: 170% -&gt; 182% -&gt; 194% -&gt; 204% -&gt; 212% (L1-5 Max)
+TP Cost: 24 -&gt; 28 -&gt; 32 -&gt; 35 -&gt; 38   |   Speed: 0.85x</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3657,6 +3857,12 @@
           <t>Increase own physical evasion rate.</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Evasion: +10% -&gt; +13% -&gt; +16% -&gt; +18% -&gt; +20% (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3677,6 +3883,12 @@
           <t>Cure status ailments for a single ally.</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Cures: poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep
+TP Cost: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3697,6 +3909,12 @@
           <t>Increase own accuracy.</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Accuracy: +15% -&gt; +17 -&gt; +19 -&gt; +21 -&gt; +23 -&gt; +25 -&gt; +26 -&gt; +27 -&gt; +28 -&gt; +30% (L10)
+Turns: 5 -&gt; 9   |   TP Cost: 5 -&gt; 8 -&gt; 11 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3717,6 +3935,12 @@
           <t>Increase own speed.</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Speed increase: 10% -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17 -&gt; 18 -&gt; 20% (L10)
+Turns: 3 (Lv1-3) -&gt; 4 (Lv4-6) -&gt; 5 (Lv7-9) -&gt; 6 (L10)   |   TP Cost: 14 (+2/Lv) -&gt; 32</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3737,6 +3961,12 @@
           <t>Increase own physical evasion rate and magical evasion rate.</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Physical evasion: +15% (+2-3%/Lv) -&gt; +25%   |   Magic evasion: +10% (+2-3%/Lv) -&gt; +20%
+Turns: 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7   |   TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20   |   Speed: 0.9x</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3757,6 +3987,12 @@
           <t>Short-range skill. Attack one enemy. May cause sleep.</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ATK: 116% -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 150 -&gt; 156% (L10)
+Sleep: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3777,6 +4013,12 @@
           <t>Short-range skill. Attack one enemy. May silence.</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ATK: 116% -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 150 -&gt; 156% (L10)
+Silence: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3797,6 +4039,12 @@
           <t>Short-range skill. Attack one enemy. May stun.</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ATK: 112% -&gt; 116 -&gt; 120 -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 150% (L10)
+Stun: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25   |   Speed: 0.9x</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3817,6 +4065,12 @@
           <t>Bow/gun skill. Attack one enemy multiple times with escalating crit rate.</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Number of attacks: 3 (Lv1-4) -&gt; 4 (Lv5-8) -&gt; 5 (L9-10)   |   ATK: 104% -&gt; 148%
+Power decrease: 25% -&gt; 14%   |   TP Cost: 30 (+4-6/Lv) -&gt; 72   |   Speed: 0.75x -&gt; 0.85x</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3837,6 +4091,12 @@
           <t>Bow/gun skill. Fire a single shot certain to hit one enemy.</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ATK: 114% -&gt; 118% -&gt; 122% -&gt; 126% -&gt; 130% (L1-5 Max)
+TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16   |   Speed: 1x -&gt; 1.12x</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3857,6 +4117,12 @@
           <t>Bow skill. Shoot a powerful single shot at one enemy for stab damage.</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Damage: 3.3x -&gt; 3.45x -&gt; 3.6x -&gt; 3.8x -&gt; 4x (L1-5 Max)   |   ATK: 88%
+TP Cost: 42 -&gt; 50 -&gt; 57 -&gt; 63 -&gt; 68   |   Speed: 0.4x</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3877,6 +4143,12 @@
           <t>Bow/gun skill. Attack one enemy. May poison.</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ATK: 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170% (L10)
+Poison: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 7 (+2/Lv) -&gt; 25</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3897,6 +4169,12 @@
           <t>Bow skill. Deal stab damage to one enemy. May freeze.</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ATK: 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170% (L10)
+Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 8 (+2/Lv) -&gt; 26</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3917,6 +4195,12 @@
           <t>Bow skill. Deal stab damage to one enemy. May paralyze.</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ATK: 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170% (L10)
+Paralysis: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 8 (+2/Lv) -&gt; 26</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3937,6 +4221,12 @@
           <t>Bow skill. Deal stab damage to one enemy. May slow.</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ATK: 116% -&gt; 122 -&gt; 128 -&gt; 134 -&gt; 140 -&gt; 145 -&gt; 150 -&gt; 155 -&gt; 160 -&gt; 165% (L10)
+Slow: 20% (+3-4%/Lv) -&gt; 50%   |   TP Cost: 9 (+2/Lv) -&gt; 27   |   Speed: 0.95x</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3957,6 +4247,12 @@
           <t>Bow skill. Shoot a barrage of arrows that rains upon all enemies.</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ATK: 84% -&gt; 88 -&gt; 92 -&gt; 96 -&gt; 100 -&gt; 103 -&gt; 106 -&gt; 109 -&gt; 112 -&gt; 115% (L10)
+TP Cost: 20 -&gt; 23 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48   |   Speed: 0.65x</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3977,6 +4273,12 @@
           <t>Bow skill. Shower enemies with a rain of arrows across multiple turns.</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ATK: 100% -&gt; 102 -&gt; 104 -&gt; 106 -&gt; 108 -&gt; 110 -&gt; 112 -&gt; 114 -&gt; 117 -&gt; 120% (L10)
+1-3 hits   |   Turns: 2 (Lv1-9) -&gt; 3 (L10 Max)   |   TP Cost: 35 (+3/Lv) -&gt; 62</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3997,6 +4299,12 @@
           <t>Bow skill. Deal stab damage to one enemy and pierce to the back row.</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ATK: 130% -&gt; 144 -&gt; 158 -&gt; 171 -&gt; 184 -&gt; 196 -&gt; 207 -&gt; 217 -&gt; 226 -&gt; 234% (L10)
+Critical rate: 5% (+1-3%/Lv) -&gt; 25%   |   TP Cost: 24 (+3-4/Lv) -&gt; 55   |   Speed: 0.7x</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4017,6 +4325,12 @@
           <t>Projectile skill. Attack and decrease speed for an enemy row.</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ATK: 94% (+3-6%/Lv) -&gt; 130% | Speed decrease chance: 30% -&gt; 75% | Speed decrease: 10%
+Turns: 4   |   TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4037,6 +4351,12 @@
           <t>Deal bash damage to one enemy. May stun.</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ATK: 120% -&gt; 126 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 154 -&gt; 162 -&gt; 170 -&gt; 180 -&gt; 192% (L10)
+Stun: 10% -&gt; 20%   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4057,6 +4377,12 @@
           <t>Identify unknown items.</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Identification success rate: 32% -&gt; 44% -&gt; 56% -&gt; 68% -&gt; 80% (L1-5 Max)
+TP Cost: 10 -&gt; 8 -&gt; 6 -&gt; 4 -&gt; 2</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4077,6 +4403,12 @@
           <t>Briefly sacrifice magic accuracy to increase magic damage.</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Magic damage: +38% -&gt; +42% -&gt; +47% -&gt; +53% -&gt; +60% (L1-5 Max)
+Magic accuracy: -2% (-2%/Lv)   |   Turns: 6   |   TP Cost: 20 -&gt; 23 -&gt; 26 -&gt; 29 -&gt; 32</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4097,6 +4429,12 @@
           <t>Mace skill. Deal bash damage with an inexorable thud.</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Damage: 2x -&gt; 2.2 -&gt; 2.4 -&gt; 2.6 -&gt; 2.8 -&gt; 3 -&gt; 3.25 -&gt; 3.5 -&gt; 3.75 -&gt; 4x (L10)
+Accuracy: +10% (+2-4%/Lv) -&gt; +30%   |   ATK: 82%   |   TP Cost: 28 (+4/Lv) -&gt; 64</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4117,6 +4455,12 @@
           <t>Mace skill. Decrease the enemy's DEF as you attack.</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ATK: 135% -&gt; 147 -&gt; 159 -&gt; 171 -&gt; 183 -&gt; 193 -&gt; 203 -&gt; 213 -&gt; 220 -&gt; 225%   |   DEF: -10%
+Turns: 4   |   TP Cost: 25 -&gt; 29 -&gt; 33 -&gt; 37 -&gt; 41 -&gt; 45 -&gt; 48 -&gt; 51 -&gt; 54 -&gt; 57</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4137,6 +4481,12 @@
           <t>Sword skill. Deal slash damage to all enemies.</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ATK: 120% -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 144 -&gt; 148 -&gt; 154 -&gt; 160% (L10)
+TP Cost: 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 57 -&gt; 62 -&gt; 67 -&gt; 73 -&gt; 79</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4157,6 +4507,12 @@
           <t>Reduce magic damage taken for the party.</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Damage reduction: 18% -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 36% (L10)
+Turns: 4 -&gt; 7   |   TP Cost: 22 -&gt; 25 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50 -&gt; 56</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4177,6 +4533,12 @@
           <t>Transform to increase own overall stats.</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Stat: +20% -&gt; +23% -&gt; +26% -&gt; +29% -&gt; +32% (L1-5 Max)
+Turns: 4 -&gt; 4 -&gt; 5 -&gt; 5 -&gt; 6   |   TP Cost: 52 -&gt; 60 -&gt; 70 -&gt; 80 -&gt; 92   |   Speed: 1.25x</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4197,6 +4559,12 @@
           <t>Short-range skill. Perform a powerful lightning strike to one enemy.</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ATK: 136% -&gt; 142 -&gt; 148 -&gt; 155 -&gt; 162 -&gt; 172 -&gt; 182 -&gt; 193 -&gt; 204 -&gt; 216% (L10)
+Accuracy: +10% (+1-2%/Lv) -&gt; +20%   |   TP Cost: 13 (+3-4/Lv) -&gt; 45   |   Speed: 0.9x -&gt; 1x</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4217,6 +4585,12 @@
           <t>Tome skill. RES-based bash damage to one enemy. May freeze/silence.</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ATK: 150% -&gt; 162 -&gt; 174 -&gt; 186 -&gt; 198 -&gt; 208 -&gt; 218 -&gt; 228 -&gt; 236 -&gt; 244% (L10)
+Freeze: 20% (+3-4%/Lv) -&gt; 50%   |   Silence: 20% -&gt; 50%   |   TP Cost: 9 (+3/Lv) -&gt; 36</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4237,6 +4611,12 @@
           <t>Protect allies from gas and damage traps.</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Turns: 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24
+TP Cost: 24 -&gt; 28 -&gt; 32 -&gt; 36 -&gt; 40 -&gt; 43 -&gt; 46 -&gt; 49 -&gt; 52 -&gt; 55</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4257,6 +4637,7 @@
           <t>Detect how many unopened treasure chests are left on the current floor.</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4277,6 +4658,11 @@
           <t>Heal an ally's HP.</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>HP recovery: 12% -&gt; 15% -&gt; 18% -&gt; 21% -&gt; 25% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4297,6 +4683,12 @@
           <t>Heal an ally's TP.</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>TP recovery: 10% -&gt; 11% -&gt; 12% -&gt; 13% -&gt; 15% (L1-5 Max)
+Speed: 0.85x</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4317,6 +4709,11 @@
           <t>Distribute all of one's TP to the target.</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>TP transfer bonus: 100% -&gt; 110% -&gt; 120% -&gt; 130% -&gt; 140% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4337,6 +4734,12 @@
           <t>Clean one's surroundings in order to increase mobility.</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Speed increase: 12% -&gt; 14% -&gt; 16% -&gt; 18% -&gt; 20% (L1-5 Max)
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4357,6 +4760,12 @@
           <t>Recover some TP.</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>TP recovery: 16% -&gt; 18% -&gt; 20% -&gt; 22% -&gt; 25% (L1-5 Max)
+Speed: 0.9x</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4377,6 +4786,12 @@
           <t>Dance skill. Lower all enemies' ATK while dance lasts.</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ATK: -4% -&gt; -6 -&gt; -8 -&gt; -10 -&gt; -11 -&gt; -12 -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16% (L10)
+Speed: 0.75x</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4397,6 +4812,12 @@
           <t>Dance skill. Lower all enemies' DEF while dance lasts.</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>DEF: -5% -&gt; -7 -&gt; -9 -&gt; -11 -&gt; -13 -&gt; -15 -&gt; -17 -&gt; -19 -&gt; -21 -&gt; -23% (L10)
+Speed: 0.75x</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4417,6 +4838,12 @@
           <t>Dance skill. Lower all enemies' accuracy while dance lasts.</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Accuracy: -4% -&gt; -5 -&gt; -6 -&gt; -7 -&gt; -8 -&gt; -9 -&gt; -10 -&gt; -11 -&gt; -12 -&gt; -13% (L10)
+Speed: 0.75x</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4437,6 +4864,12 @@
           <t>Dance skill. Lower all enemies' evasion while dance lasts.</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Evasion: -5% -&gt; -7 -&gt; -9 -&gt; -11 -&gt; -13 -&gt; -15 -&gt; -17 -&gt; -19 -&gt; -21 -&gt; -23% (L10)
+Speed: 0.75x</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4457,6 +4890,12 @@
           <t>Dance skill. Damage all enemies at the start of user's turn while dance lasts.</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Max HP damage: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)
+Total damage cap: 250 -&gt; 275 -&gt; 300 -&gt; 325 -&gt; 350 -&gt; 375 -&gt; 400 -&gt; 430 -&gt; 460 -&gt; 500</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4477,6 +4916,12 @@
           <t>Dance skill. Lower all enemies' speed while dance lasts.</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Speed decrease: 5% -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14% (L10)
+Speed: 0.75x</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4497,6 +4942,12 @@
           <t>Dance skill. Lower all enemies' elemental resistances while dance lasts.</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Resistance decrease: 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25 (L10)
+Speed: 0.75x</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4517,6 +4968,12 @@
           <t>Whip skill. Deal bash damage to an enemy row from mid-range.</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ATK: 120% -&gt; 124 -&gt; 128 -&gt; 132 -&gt; 136 -&gt; 140 -&gt; 145 -&gt; 150 -&gt; 155 -&gt; 160% (L10)
+Power decrease: 10%   |   TP Cost: 22 (+3-4/Lv) -&gt; 50   |   Speed: 0.75x -&gt; 0.85x</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4537,6 +4994,12 @@
           <t>Whip skill. Attack one enemy 1-5 times from mid-range.</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ATK: 107% -&gt; 114% -&gt; 121% -&gt; 128% -&gt; 136% (L1-5 Max)
+TP Cost: 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46   |   Speed: 0.75x -&gt; 0.8x</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4557,6 +5020,12 @@
           <t>Whip skill. Deal bash damage to one enemy twice. May silence/paralyze.</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ATK: 135% -&gt; 142% -&gt; 149% -&gt; 157% -&gt; 165% (L1-5 Max)   |   Silence: 25% (+3%/Lv)
+Paralysis: 20% -&gt; 23% -&gt; 26% -&gt; 29% -&gt; 32%   |   TP Cost: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4577,6 +5046,12 @@
           <t>Attack 0-4 times on random targets.</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ATK: 104% -&gt; 108 -&gt; 112 -&gt; 116 -&gt; 120 -&gt; 124 -&gt; 127 -&gt; 130 -&gt; 133 -&gt; 136% (L10)
+Accuracy: +20%   |   TP Cost: 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 40 -&gt; 44 -&gt; 48 -&gt; 52 -&gt; 56 -&gt; 60</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4597,6 +5072,12 @@
           <t>Take a break to heal own HP and raise Pep.</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>HP recovery: 20% -&gt; 25% -&gt; 30% -&gt; 35% -&gt; 40% (L1-5 Max)
+TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4617,6 +5098,7 @@
           <t>Spin the magic roulette. Nobody knows what will happen.</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4637,6 +5119,12 @@
           <t>Attack one enemy. May instakill.</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ATK: 120% -&gt; 126 -&gt; 132 -&gt; 138 -&gt; 142 -&gt; 150 -&gt; 158 -&gt; 168 -&gt; 178 -&gt; 190% (L10)
+Instakill: 15% (+1-2%/Lv) -&gt; 25%   |   TP Cost: 17 (+2/Lv) -&gt; 35   |   Speed: 0.88x</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4657,6 +5145,12 @@
           <t>50/50 chance of non-elemental damage to each enemy. May stun.</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ATK: 95% -&gt; 99 -&gt; 103 -&gt; 107 -&gt; 111 -&gt; 115 -&gt; 119 -&gt; 123 -&gt; 127 -&gt; 131% (L10)
+Stun: 40% (+3-4%/Lv) -&gt; 70%   |   TP Cost: 32 (+2/Lv) -&gt; 50   |   Speed: 0.65x</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4677,6 +5171,12 @@
           <t>Increase own ATK at the price of lowering own DEF.</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ATK: 15% (+5%/Lv) -&gt; 35% (L5 Max)   |   DEF: -11% -&gt; -14% -&gt; -17% -&gt; -21% -&gt; -25%
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4697,6 +5197,7 @@
           <t>Open a magic box. Nobody knows what will happen.</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4717,6 +5218,12 @@
           <t>Turn a weakened enemy into food. Ineffective against some enemies.</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Conversion success: 35% -&gt; 42% -&gt; 49% -&gt; 57% -&gt; 65% (L1-5 Max)
+TP Cost: 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32   |   Speed: 0.85x</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4737,6 +5244,12 @@
           <t>Deal non-elemental damage to all enemies with a storm of roses. May poison.</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ATK: 118% -&gt; 125 -&gt; 132 -&gt; 139 -&gt; 146 -&gt; 152 -&gt; 158 -&gt; 164 -&gt; 170 -&gt; 176% (L10)
+Poison: 50% (+3-4%/Lv) -&gt; 80%   |   TP Cost: 22 (+4/Lv) -&gt; 58   |   Speed: 0.6x -&gt; 0.7x</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4757,6 +5270,12 @@
           <t>Fan skill. Deal bashing damage to one enemy. May delay enemy turn.</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>ATK: 150% -&gt; 162 -&gt; 174 -&gt; 186 -&gt; 198 -&gt; 208 -&gt; 218 -&gt; 228 -&gt; 240 -&gt; 256% (L10)
+Turn delay rate: 25% (+2%/Lv)   |   TP Cost: 10 (+2-3/Lv) -&gt; 32   |   Speed: 0.95x</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4777,6 +5296,12 @@
           <t>Fan skill. With increased ATK, deal long-range damage to one enemy.</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ATK: 120%
+Speed: 1.15x</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4797,6 +5322,12 @@
           <t>Short-range skill. Pierce through to the back row with stab damage. May slow.</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ATK: 130% (+8%/Lv) -&gt; 202% (L10 Max)   |   Slow: 25% -&gt; 45%   |   Accuracy: -5% (+2%/Lv)
+TP Cost: 24 -&gt; 27 -&gt; 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 -&gt; 45 -&gt; 48 -&gt; 50   |   Speed: 0.75x</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4817,6 +5348,12 @@
           <t>Short-range skill. Attack one enemy and reduce target's max HP.</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ATK: 88% -&gt; 92% -&gt; 97% -&gt; 103% -&gt; 110% (L1-5 Max)   |   Max HP reduction: 50% -&gt; 100%
+Turns: 6   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 23 -&gt; 25   |   Speed: 0.85x</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4837,6 +5374,12 @@
           <t>Convert current DEF to bonus ATK (DEF becomes 0).</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>DEF conversion bonus: 60% -&gt; 80% -&gt; 100% -&gt; 125% -&gt; 150% (L1-5 Max)
+Turns: 2   |   TP Cost: 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50   |   Speed: 1.15x</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4857,6 +5400,7 @@
           <t>Something emerges from the shadows. Nobody knows what will happen.</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4877,6 +5421,12 @@
           <t>Whip skill. Attack one enemy 1-3 times from mid-range. Crits against Beasts.</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ATK: 118% -&gt; 122 -&gt; 126 -&gt; 130 -&gt; 134 -&gt; 138 -&gt; 142 -&gt; 145 -&gt; 148 -&gt; 151% (L10)
+Accuracy UP   |   TP Cost: 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4897,6 +5447,12 @@
           <t>Summon Spartan for short-range bash damage.</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ATK: 144% -&gt; 147 -&gt; 150 -&gt; 154 -&gt; 158 -&gt; 162 -&gt; 166 -&gt; 170 -&gt; 175 -&gt; 180% (L10)
+Turns: 3 (Lv1-3) -&gt; 4 (Lv4-6) -&gt; 5 (Lv7-9) -&gt; 6 (L10)   |   TP Cost: 20 -&gt; 42</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4917,6 +5473,12 @@
           <t>Summon Oracles for mid-range INT-based damage and possible paralysis.</t>
         </is>
       </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ATK: 126% (+2-5%/Lv) -&gt; 157%   |   Paralysis: 30% (+3-5%/Lv) -&gt; 64% (L10)
+Turns: 3 (Lv1-4) -&gt; 4 (Lv5-8) -&gt; 5 (Lv9-10)   |   TP Cost: 24 -&gt; 48   |   Speed: 0.9x</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4937,6 +5499,12 @@
           <t>Summon Catalina to heal allies' HP.</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Heal Power: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12 (L1-5 Max)
+Turns: 3 (Lv1-2) -&gt; 4 (Lv3-4) -&gt; 5 (L5 Max)   |   TP Cost: 30 -&gt; 48   |   Speed: 0.9x</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4957,6 +5525,12 @@
           <t>Summon Mercidarian for random long-range stab damage to all foes.</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>ATK: 100% -&gt; 104 -&gt; 108 -&gt; 112 -&gt; 118 -&gt; 123 -&gt; 128 -&gt; 133 -&gt; 138 -&gt; 143% (L10)
+Turns: 2 (Lv1-4) -&gt; 3 (Lv5-7) -&gt; 4 (Lv8-10)   |   TP Cost: 42 -&gt; 70   |   Speed: 0.75x</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4977,6 +5551,12 @@
           <t>Summon Perdurabo to cure two allies' status ailments.</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Cures: poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; petrify &gt; slow &gt; all debuffs
+Duration: 5   |   TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32 -&gt; 34 -&gt; 38   |   Speed: 1.15x</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4997,6 +5577,12 @@
           <t>Summon Musiy for immediate single-target attack magic.</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Pwr: 180 -&gt; 240 -&gt; 310 -&gt; 390 -&gt; 480 -&gt; 585 -&gt; 700 (L7 Max)
+Turns: 4   |   TP Cost: 38 (+4-6/Lv) -&gt; 68   |   Speed: 0.82x -&gt; 0.92x</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5017,6 +5603,12 @@
           <t>Actual course of action</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5037,6 +5629,12 @@
           <t>Actual course of action</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5057,6 +5655,12 @@
           <t>Actual course of action</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5077,6 +5681,12 @@
           <t>Actual course of action</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5097,6 +5707,12 @@
           <t>Actual course of action</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5117,6 +5733,12 @@
           <t>Actual course of action</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5137,6 +5759,12 @@
           <t>Actual course of action</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5157,6 +5785,12 @@
           <t>Poison all enemies.</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5177,6 +5811,12 @@
           <t>Freeze all enemies.</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5197,6 +5837,12 @@
           <t>Paralyze all enemies.</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5217,6 +5863,12 @@
           <t>Silence all enemies.</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5237,6 +5889,12 @@
           <t>Slow all enemies.</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5257,6 +5915,12 @@
           <t>Heal one random ally for 20% of HP and TP.</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5277,6 +5941,12 @@
           <t>Fully heal one enemy.</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5297,6 +5967,12 @@
           <t>Deal own level x10 damage to one random ally or enemy.</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5317,6 +5993,12 @@
           <t>Nothing happens.</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5337,6 +6019,12 @@
           <t>Deal damage equal to own remaining HP - 1 to one random ally or enemy.</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5357,6 +6045,12 @@
           <t>A long-range + stab attack to all enemies. Inflicted damage is based off the practitioner's ATK</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5377,6 +6071,12 @@
           <t>Song, dance, doll, and chant are canceled for all enemies and allies.</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5397,6 +6097,12 @@
           <t>Recover 75TP for the party.</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5417,6 +6123,12 @@
           <t>An unknown dog (Genjimaru) appeared for support.</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5437,6 +6149,12 @@
           <t>Attack oneself with own ATK.</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5457,6 +6175,12 @@
           <t>Acquire the total amount of money for beating all enemies there x4.</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5477,6 +6201,12 @@
           <t>Inflict a fixed damage of 666 to someone from your enemies or allies.</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5497,6 +6227,12 @@
           <t>Nothing happens.</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5517,6 +6253,12 @@
           <t>Instant death for the practitioner</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5537,6 +6279,12 @@
           <t>Recover 200HP for the party.</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5557,6 +6305,12 @@
           <t>Circle Brave and Circle Protect activated for an ally.</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5577,6 +6331,12 @@
           <t>Fully recover HP for the one with the highest rate of TP loss out of your allies.</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5597,6 +6357,12 @@
           <t>Stab, Cut, and Bash Protect Lv5 activated for the party.</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5617,6 +6383,12 @@
           <t>Stun the party.</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5637,6 +6409,12 @@
           <t>Put the party to sleep. (Guaranteed without perfect sleep resistance.)</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5657,6 +6435,12 @@
           <t>Silence + freeze + slow for all enemies.</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5677,6 +6461,12 @@
           <t>HP gets cut down to half for the party.</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5697,6 +6487,12 @@
           <t>Aim and Fleet Foot Lv10 activated for the party.</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5717,6 +6513,12 @@
           <t>HP and TP fully recovered for all enemies and allies.</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5737,6 +6539,12 @@
           <t>Enemies will flee.</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5757,6 +6565,12 @@
           <t>Scatter 1/10 of pocket money your ally has.</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5777,6 +6591,12 @@
           <t>Attack an enemy 7 times with own ATK.</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5797,6 +6617,12 @@
           <t>Nothing happens.</t>
         </is>
       </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5817,6 +6643,12 @@
           <t>Damage one enemy for a percentage of HP.</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5837,6 +6669,12 @@
           <t>Heal one enemy for a percentage of HP.</t>
         </is>
       </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5857,6 +6695,12 @@
           <t>Deal fire damage to one enemy.</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
+Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5877,6 +6721,12 @@
           <t>Deal fire damage to an enemy row.</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
+Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5897,6 +6747,12 @@
           <t>Deal fire damage to all enemies.</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
+Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5917,6 +6773,12 @@
           <t>Deal tremendous fire damage to one enemy.</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max)   |   Accuracy: 82% (+2%/Lv)
+TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5937,6 +6799,12 @@
           <t>Deal water damage to one enemy.</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
+Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5957,6 +6825,12 @@
           <t>Deal water damage to an enemy row.</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
+Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5977,6 +6851,12 @@
           <t>Deal water damage to all enemies.</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
+Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5997,6 +6877,12 @@
           <t>Deal tremendous water damage to one enemy.</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max)   |   Accuracy: 82% (+2%/Lv)
+TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6017,6 +6903,12 @@
           <t>Deal lightning damage to one enemy.</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
+Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6037,6 +6929,12 @@
           <t>Deal lightning damage to an enemy row.</t>
         </is>
       </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
+Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6057,6 +6955,12 @@
           <t>Deal lightning damage to all enemies.</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
+Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6077,6 +6981,12 @@
           <t>Deal tremendous lightning damage to one enemy.</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max)   |   Accuracy: 82% (+2%/Lv)
+TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6097,6 +7007,12 @@
           <t>Deal wind damage to one enemy.</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
+Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6117,6 +7033,12 @@
           <t>Deal wind damage to an enemy row.</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
+Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6137,6 +7059,12 @@
           <t>Deal wind damage to all enemies.</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
+Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6157,6 +7085,12 @@
           <t>Deal tremendous wind damage to one enemy.</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max)   |   Accuracy: 82% (+2%/Lv)
+TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6177,6 +7111,12 @@
           <t>Deal earth damage to one enemy.</t>
         </is>
       </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Pwr: 70 -&gt; 105 -&gt; 140 -&gt; 175 -&gt; 220 -&gt; 270 -&gt; 320 -&gt; 380 -&gt; 450 -&gt; 520 (L10)
+Accuracy: 86% (+1%/Lv)   |   TP Cost: 5 (+2-4/Lv) -&gt; 32   |   Speed: 2.25x</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6197,6 +7137,12 @@
           <t>Deal earth damage to an enemy row.</t>
         </is>
       </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Pwr: 90 -&gt; 120 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 290 -&gt; 340 -&gt; 400 -&gt; 460 -&gt; 530 (L10)
+Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 15 (+4-6/Lv) -&gt; 60   |   Speed: 1.7x</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6217,6 +7163,12 @@
           <t>Deal earth damage to all enemies.</t>
         </is>
       </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Pwr: 300 -&gt; 350 -&gt; 400 -&gt; 450 -&gt; 500 -&gt; 550 -&gt; 590 -&gt; 650 -&gt; 690 -&gt; 750 (L10)
+Accuracy: 75% (+1-2%/Lv) -&gt; 85%   |   TP Cost: 42 (+6-10/Lv) -&gt; 120   |   Speed: 1.3x</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6237,6 +7189,12 @@
           <t>Deal tremendous earth damage to one enemy.</t>
         </is>
       </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Pwr: 620 -&gt; 760 -&gt; 920 -&gt; 1100 -&gt; 1300 (L1-5 Max)   |   Accuracy: 82% (+2%/Lv)
+TP Cost: 40 -&gt; 50 -&gt; 60 -&gt; 72 -&gt; 84   |   Speed: 1.5x   |   Chant: 0.75x -&gt; 0.7x</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6257,6 +7215,12 @@
           <t>Deal non-elemental damage to one enemy to regain HP.</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Pwr: 60 -&gt; 95 -&gt; 130 -&gt; 165 -&gt; 200 -&gt; 230 -&gt; 260 -&gt; 290 -&gt; 320 -&gt; 350 (L10)
+Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   HP Absorb: 100%   |   TP Cost: 9 (+1/Lv) -&gt; 18</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6277,6 +7241,12 @@
           <t>Deal non-elemental damage to one enemy to regain TP.</t>
         </is>
       </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Pwr: 22 -&gt; 30 -&gt; 38 -&gt; 46 -&gt; 54 -&gt; 60 -&gt; 66 -&gt; 72 -&gt; 78 -&gt; 82   |   Accuracy: 80% -&gt; 90%
+TP Absorb: 100% | TP Cost: 6 (+1/Lv) -&gt; 15 | Speed: 1.75x | Chant: 1.25x -&gt; 1.07x</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6297,6 +7267,12 @@
           <t>Raise max HP.</t>
         </is>
       </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Max HP increase rate: 20% -&gt; 28% -&gt; 36% -&gt; 45% -&gt; 50% (L1-5 Max)
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 27 -&gt; 31 -&gt; 35 -&gt; 39 -&gt; 43   |   Speed: 1.5x</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6317,6 +7293,12 @@
           <t>Absorb HP from an enemy row.</t>
         </is>
       </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Pwr: 75 (+35-45/Lv) -&gt; 450   |   Accuracy: 65% (+2-3%/Lv) -&gt; 87%   |   HP Absorb: 100%
+TP Cost: 18 -&gt; 21 -&gt; 24 -&gt; 27 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42 -&gt; 46 -&gt; 50   |   Speed: 1.5x</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6337,6 +7319,12 @@
           <t>Stun one enemy.</t>
         </is>
       </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Accuracy: 65% -&gt; 68% -&gt; 71% -&gt; 73% -&gt; 75% (L1-5 Max)
+TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18   |   Speed: 0.8x -&gt; 0.92x   |   Chant: 1.25x</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6357,6 +7345,12 @@
           <t>Poison all enemies.</t>
         </is>
       </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Accuracy: 75% -&gt; 78% -&gt; 81% -&gt; 83% -&gt; 85% (L1-5 Max)
+TP Cost: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   Speed: 2.15x   |   Chant: 1.2x -&gt; 1.4x</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6377,6 +7371,12 @@
           <t>Freeze all enemies.</t>
         </is>
       </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Accuracy: 70% -&gt; 72% -&gt; 74% -&gt; 76% -&gt; 78% (L1-5 Max)
+TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6397,6 +7397,12 @@
           <t>Paralyze all enemies.</t>
         </is>
       </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Accuracy: 65% -&gt; 68% -&gt; 71% -&gt; 73% -&gt; 75% (L1-5 Max)
+TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1x -&gt; 1.2x</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6417,6 +7423,12 @@
           <t>Put an enemy row to sleep.</t>
         </is>
       </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Accuracy: 65% -&gt; 68% -&gt; 71% -&gt; 73% -&gt; 75% (L1-5 Max)
+TP Cost: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18   |   Chant: 0.75x -&gt; 0.87x</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6437,6 +7449,12 @@
           <t>Silence all enemies.</t>
         </is>
       </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Accuracy: 70% -&gt; 72% -&gt; 74% -&gt; 76% -&gt; 78% (L1-5 Max)
+TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6457,6 +7475,12 @@
           <t>Petrify an enemy row.</t>
         </is>
       </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Accuracy: 70% -&gt; 72% -&gt; 74% -&gt; 76% -&gt; 78% (L1-5 Max)
+TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23   |   Chant: 0.75x -&gt; 0.87x</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6477,6 +7501,12 @@
           <t>Instakill one enemy.</t>
         </is>
       </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Accuracy: 50% -&gt; 52% -&gt; 55% -&gt; 58% -&gt; 60% (L1-5 Max)
+TP Cost: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20   |   Chant: 0.75x -&gt; 0.87x</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6497,6 +7527,12 @@
           <t>Slow an enemy row.</t>
         </is>
       </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Accuracy: 50% -&gt; 55% -&gt; 60% -&gt; 64% -&gt; 68% (L1-5 Max)
+TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23   |   Chant: 1x -&gt; 1.12x</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6517,6 +7553,12 @@
           <t>Stun an enemy row.</t>
         </is>
       </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Accuracy: 54% -&gt; 58% -&gt; 62% -&gt; 66% -&gt; 70% (L1-5 Max)
+TP Cost: 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30   |   Speed: 0.4x -&gt; 0.5x   |   Chant: 1.25x</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6537,6 +7579,12 @@
           <t>Negate buffs for all enemies.</t>
         </is>
       </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Accuracy: 55% -&gt; 65% -&gt; 75% -&gt; 85% -&gt; 95% (L1-5 Max)   |   Buff cancel rate: 100%
+TP Cost: 8 -&gt; 11 -&gt; 14 -&gt; 18 -&gt; 22   |   Speed: 1.25x   |   Chant: 1.25x -&gt; 1.45x</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6557,6 +7605,12 @@
           <t>Deal non-elemental damage to all enemies (effective vs. unholy monsters).</t>
         </is>
       </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Pwr: 250 (+40-50/Lv) -&gt; 640   |   Accuracy: 60% -&gt; 70%   |   Damage vs. unholy: +100%
+TP Cost: 45 -&gt; 52 -&gt; 59 -&gt; 66 -&gt; 74 -&gt; 80 -&gt; 86 -&gt; 90 -&gt; 95 -&gt; 100   |   Speed: 1.75x</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6577,6 +7631,12 @@
           <t>Imbue an ally's weapon with fire.</t>
         </is>
       </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max)   |   TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
+Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6597,6 +7657,12 @@
           <t>Imbue an ally's weapon with water.</t>
         </is>
       </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max)   |   TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
+Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6617,6 +7683,12 @@
           <t>Imbue an ally's weapon with lightning.</t>
         </is>
       </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max)   |   TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
+Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6637,6 +7709,12 @@
           <t>Imbue an ally's weapon with wind.</t>
         </is>
       </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max)   |   TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
+Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6657,6 +7735,12 @@
           <t>Imbue an ally's weapon with earth.</t>
         </is>
       </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 (L1-5 Max)   |   TP Cost: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10
+Speed: 1.5x -&gt; 1.7x   |   Chant: 1.75x -&gt; 2.25x</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6677,6 +7761,12 @@
           <t>Raise one row of allies' resistance to stab damage.</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Resistance: 20 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6697,6 +7787,12 @@
           <t>Raise one row of allies' resistance to slash damage.</t>
         </is>
       </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Resistance: 18 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6717,6 +7813,12 @@
           <t>Raise one row of allies' resistance to bash damage.</t>
         </is>
       </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Resistance: 18 -&gt; 24 -&gt; 28 -&gt; 32 -&gt; 36 (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6737,6 +7839,12 @@
           <t>Heal an ally's HP.</t>
         </is>
       </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Heals RES: 4x (+1x/Lv) -&gt; 13x (L10 Max)   |   Heal Cap: 100 (+60-80/Lv) -&gt; 800
+TP Cost: 3 -&gt; 5 -&gt; 7 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 17 -&gt; 20 -&gt; 23 -&gt; 26   |   Speed: 1.75x</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6757,6 +7865,12 @@
           <t>Heal the party's HP.</t>
         </is>
       </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Heals RES: 2.5x (+0.5x/Lv) -&gt; 7x (L10 Max)   |   Heal Cap: 80 (+50-60/Lv) -&gt; 600
+TP Cost: 15 -&gt; 20 -&gt; 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 46 -&gt; 52 -&gt; 58 -&gt; 64   |   Speed: 1.35x</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6777,6 +7891,11 @@
           <t>Fully heal one ally's HP.</t>
         </is>
       </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>TP Cost: 48 -&gt; 45 -&gt; 42 -&gt; 39 -&gt; 36 (L1-5 Max)   |   Speed: 1.15x   |   Chant: 1.5x -&gt; 1.75x</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6797,6 +7916,12 @@
           <t>Cure status ailments for a single ally.</t>
         </is>
       </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Cures: poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; petrify &gt; slow &gt; all debuffs
+TP Cost: 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   Speed: 2.25x   |   Chant: 2.75x</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6817,6 +7942,12 @@
           <t>Cure party's status ailments.</t>
         </is>
       </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Cures: poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; petrify &gt; slow &gt; all debuffs
+TP Cost: 9 -&gt; 12 -&gt; 15 -&gt; 18 -&gt; 21 -&gt; 25 -&gt; 30 -&gt; 36   |   Speed: 1.5x   |   Chant: 2x</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6837,6 +7968,12 @@
           <t>Revive a dead ally.</t>
         </is>
       </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>HP on revival: 40% -&gt; 52% -&gt; 64% -&gt; 76% -&gt; 88% (L1-5 Max)
+TP Cost: 26 -&gt; 30 -&gt; 34 -&gt; 38 -&gt; 42   |   Speed: 1.25x   |   Chant: 1.3x -&gt; 1.5x</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6857,6 +7994,12 @@
           <t>Raise an ally's ATK.</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>ATK: +10% -&gt; +13% -&gt; +16% -&gt; +19% -&gt; +22% (L1-5 Max)
+Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17   |   Chant: 1.25x</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6877,6 +8020,12 @@
           <t>Raise an ally's DEF.</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>DEF: +10% -&gt; +14% -&gt; +18% -&gt; +22% -&gt; +25% (L1-5 Max)
+Turns: 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9   |   TP Cost: 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17   |   Chant: 1.25x</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6897,6 +8046,12 @@
           <t>Raise the party's magic defense.</t>
         </is>
       </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Magic defense: +10% -&gt; +12% -&gt; +14% -&gt; +16% -&gt; +18% (L1-5 Max)
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32   |   Chant: 1.25x</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6917,6 +8072,12 @@
           <t>Raise the party's resistance to fire, water, lightning, wind, and earth.</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Elemental resistance increase: 5 -&gt; 10 -&gt; 15 -&gt; 20 -&gt; 25 (L1-5 Max)
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 16 -&gt; 20 -&gt; 24 -&gt; 28 -&gt; 32   |   Chant: 1.25x</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6937,6 +8098,12 @@
           <t>Raise an ally's speed.</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Speed increase: 8% -&gt; 9% -&gt; 10% -&gt; 11% -&gt; 12% (L1-5 Max)
+Turns: 3   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Speed: 1.25x -&gt; 1.41x</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6957,6 +8124,12 @@
           <t>Raise an ally's max HP.</t>
         </is>
       </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Max HP: +20% -&gt; +23 -&gt; +26 -&gt; +29 -&gt; +32 -&gt; +35 -&gt; +38 -&gt; +41 -&gt; +44 -&gt; +47% (L10)
+Turns: 5 -&gt; 5 -&gt; 6 -&gt; 6 -&gt; 7 -&gt; 7 -&gt; 8 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 18 (+3/Lv) -&gt; 45</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6977,6 +8150,12 @@
           <t>Cure one row of allies' status ailments.</t>
         </is>
       </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Cures: poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; petrify &gt; slow &gt; all debuffs
+TP Cost: 7 -&gt; 10 -&gt; 13 -&gt; 16 -&gt; 19 -&gt; 21 -&gt; 24 -&gt; 28   |   Speed: 1.75x   |   Chant: 2.25x</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6997,6 +8176,12 @@
           <t>Create 2 magical afterimages that let you dodge one attack each.</t>
         </is>
       </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Turns: 3 -&gt; 4 -&gt; 5 (L1-3 Max)   |   TP Cost: 30 -&gt; 38 -&gt; 46   |   Speed: 0.85x
+Chant: 0.75x -&gt; 0.65x</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7017,6 +8202,12 @@
           <t>Reduce incoming physical damage by a certain amount.</t>
         </is>
       </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Amount of damage reduced: 30% -&gt; 33% -&gt; 37% -&gt; 41% -&gt; 45% (L1-5 Max)
+Turns: 4   |   TP Cost: 24 -&gt; 28 -&gt; 33 -&gt; 37 -&gt; 42   |   Speed: 1.5x   |   Chant: 0.75x</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7037,6 +8228,12 @@
           <t>While active, immediately revive upon death.</t>
         </is>
       </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Amount of HP on revival: 10% -&gt; 20% -&gt; 30% -&gt; 40% -&gt; 50% (L1-5 Max)
+Turns: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10   |   TP Cost: 25 -&gt; 30 -&gt; 35 -&gt; 40 -&gt; 45   |   Speed: 1.5x</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7057,6 +8254,11 @@
           <t>Illuminate the dungeon to find hidden pathways.</t>
         </is>
       </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Turns: 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28 -&gt; 30</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7077,6 +8279,11 @@
           <t>Escape from the dungeon.</t>
         </is>
       </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>TP Cost: 28 -&gt; 21 -&gt; 14 -&gt; 7 -&gt; 1 (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7097,6 +8304,12 @@
           <t>Put an enemy to sleep.</t>
         </is>
       </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Accuracy: 70% -&gt; 73% -&gt; 76% -&gt; 79% -&gt; 82% (L1-5 Max)
+Speed: 1.5x   |   Chant: 1.5x -&gt; 1.66x</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7117,6 +8330,11 @@
           <t>Raise the party's chance of doing multiple strikes while song lasts.</t>
         </is>
       </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Speed: 1.35x   |   Chant: 1.4x</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7137,6 +8355,12 @@
           <t>Raise the party's critical rate while song lasts.</t>
         </is>
       </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Critical rate: 10% -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28% (L10)
+Speed: 1.35x   |   Chant: 1.4x -&gt; 2x</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7157,6 +8381,12 @@
           <t>Raise the party's magic attack power while song lasts.</t>
         </is>
       </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Magic attack: +10% -&gt; +11 -&gt; +12 -&gt; +13 -&gt; +14 -&gt; +15 -&gt; +16 -&gt; +17 -&gt; +18 -&gt; +20%
+Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7177,6 +8407,12 @@
           <t>Raise the party's magic defense power while song lasts.</t>
         </is>
       </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Magic defense: +10% -&gt; +11 -&gt; +12 -&gt; +13 -&gt; +14 -&gt; +15 -&gt; +16 -&gt; +17 -&gt; +18 -&gt; +20%
+Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7197,6 +8433,12 @@
           <t>Decrease the party's chant time while song lasts.</t>
         </is>
       </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Chant time: -10% -&gt; -11 -&gt; -12 -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -20%
+Speed: 1.35x   |   Chant: 1.4x -&gt; 2x</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7217,6 +8459,12 @@
           <t>Gradually heal the party's HP while song lasts.</t>
         </is>
       </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>HP recovery: 20 -&gt; 35 -&gt; 50 -&gt; 65 -&gt; 80 -&gt; 100 -&gt; 130 -&gt; 170 -&gt; 210 -&gt; 250 (L10)
+Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7237,6 +8485,12 @@
           <t>Gradually heal the party's TP while song lasts.</t>
         </is>
       </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>TP recovery: 4 -&gt; 6 -&gt; 8 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 18 -&gt; 22 -&gt; 26 -&gt; 30 (L10)
+Speed: 1.35x   |   Chant: 1.1x -&gt; 1.5x</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7257,6 +8511,12 @@
           <t>Raise the party's speed while song lasts.</t>
         </is>
       </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Speed increase: 6% -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)
+Speed: 1.35x   |   Chant: 1.1x -&gt; 1.5x</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7277,6 +8537,12 @@
           <t>Raise the party's acquired EXP while song lasts.</t>
         </is>
       </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>EXP: +16% -&gt; +17 -&gt; +18 -&gt; +19 -&gt; +20 -&gt; +21 -&gt; +22 -&gt; +23 -&gt; +24 -&gt; +25% (L10)
+Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7297,6 +8563,12 @@
           <t>Raise the party's magic accuracy while song lasts.</t>
         </is>
       </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Magic accuracy: +6% -&gt; +7 -&gt; +8 -&gt; +9 -&gt; +10 -&gt; +11 -&gt; +12 -&gt; +13 -&gt; +14 -&gt; +15%
+Speed: 1.35x   |   Chant: 1.25x -&gt; 1.7x</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7317,6 +8589,12 @@
           <t>Dodge enemy attacks by creating a shadow clone.</t>
         </is>
       </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Number of dodges: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 (L1-5 Max)
+Turns: 3 -&gt; 3 -&gt; 4 -&gt; 4 -&gt; 5   |   TP Cost: 23 -&gt; 27 -&gt; 32 -&gt; 38 -&gt; 45   |   Speed: 0.85x</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7337,6 +8615,12 @@
           <t>Disable skill usage for an enemy row. Level must exceed the target's.</t>
         </is>
       </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Shadow Sew Success: 30% -&gt; 32% -&gt; 35% -&gt; 37% -&gt; 40% (L1-5 Max)
+Turns: 3 | TP Cost: 36 -&gt; 39 -&gt; 43 -&gt; 47 -&gt; 52 | Speed: 0.8x | Chant: 0.8x -&gt; 0.88x</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7357,6 +8641,12 @@
           <t>Lower all enemies' accuracy.</t>
         </is>
       </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Accuracy: -10% -&gt; -12% -&gt; -14% -&gt; -16% -&gt; -18% (L1-5 Max)
+Turns: 3   |   TP Cost: 15 -&gt; 18 -&gt; 21 -&gt; 24 -&gt; 27   |   Chant: 1.15x -&gt; 1.3x</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7377,6 +8667,12 @@
           <t>Deal fire damage based on enemy's max HP and lower ATK to an enemy row.</t>
         </is>
       </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
+ATK: -4% (-1%/Lv) (3 Turns)   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7397,6 +8693,12 @@
           <t>Deal water damage based on enemy's max HP and lower magic def. to an enemy row.</t>
         </is>
       </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
+Magic defense: -7% -&gt; -18%   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7417,6 +8719,12 @@
           <t>Deal lightning damage based on enemy's max HP and lower speed to an enemy row.</t>
         </is>
       </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
+Speed decrease: 4% (+1%/Lv)   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7437,6 +8745,12 @@
           <t>Deal wind damage based on enemy's max HP and lower evasion to an enemy row.</t>
         </is>
       </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
+Evasion: -7% (-2%/Lv) (3 Turns)   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7457,6 +8771,12 @@
           <t>Deal earth damage based on enemy's max HP and lower DEF to an enemy row.</t>
         </is>
       </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Max HP damage: 4% -&gt; 5% -&gt; 6% -&gt; 7% -&gt; 8% (L1-5 Max)   |   Accuracy: 64% (+4%/Lv)
+DEF: -4% (-1%/Lv) (3 Turns)   |   Damage cap: 250 -&gt; 500   |   TP Cost: 20 (+5/Lv) -&gt; 40</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7477,6 +8797,12 @@
           <t>Deal non-elemental damage to an enemy row.</t>
         </is>
       </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Pwr: 350 -&gt; 390 -&gt; 430 -&gt; 470 -&gt; 510 -&gt; 550 -&gt; 590 -&gt; 630 -&gt; 680 -&gt; 720 (L10)
+Accuracy: 86% (+1%/Lv)   |   TP Cost: 22 (+4-6/Lv) -&gt; 66   |   Speed: 1.3x</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7497,6 +8823,12 @@
           <t>Deal non-elemental damage to all enemies. May stun.</t>
         </is>
       </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Pwr: 240 (+40/Lv) -&gt; 600 (L10 Max)   |   Accuracy: 76% (+1%/Lv)   |   Stun: 25%
+TP Cost: 36 -&gt; 42 -&gt; 48 -&gt; 54 -&gt; 60 -&gt; 66 -&gt; 72 -&gt; 80 -&gt; 88 -&gt; 96   |   Speed: 1.5x</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7517,6 +8849,12 @@
           <t>Raise the party's ATK.</t>
         </is>
       </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>ATK: +8% -&gt; +10% -&gt; +12% -&gt; +14% -&gt; +16% (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22   |   Chant: 1.15x</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7537,6 +8875,12 @@
           <t>Raise the party's DEF.</t>
         </is>
       </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>DEF: +8% -&gt; +10% -&gt; +12% -&gt; +14% -&gt; +16% (L1-5 Max)
+Turns: 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8   |   TP Cost: 12 -&gt; 15 -&gt; 18 -&gt; 20 -&gt; 22   |   Chant: 1.15x</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7557,6 +8901,12 @@
           <t>Create a field that reduces damage for both sides for a time.</t>
         </is>
       </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Damage reduction: 25% -&gt; 27% -&gt; 29% -&gt; 32% -&gt; 35% (L1-5 Max)
+Turns: 3   |   TP Cost: 28 -&gt; 31 -&gt; 34 -&gt; 37 -&gt; 40   |   Speed: 0.75x   |   Chant: 1.75x</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7577,6 +8927,12 @@
           <t>Raise encounter rate.</t>
         </is>
       </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Turns: 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26 -&gt; 28
+TP Cost: 12 -&gt; 11 -&gt; 10 -&gt; 9 -&gt; 8 -&gt; 7 -&gt; 6 -&gt; 5 -&gt; 4 -&gt; 3</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7597,6 +8953,12 @@
           <t>Sacrifice yourself to revive, heal, and recover status effects for the rest of the party.</t>
         </is>
       </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Heals RES: 11x -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 19 -&gt; 21 -&gt; 23 -&gt; 25x (L8)
+Recoverable status ailments: 1 (+1/Lv)   |   HP on revival: 10% (+5-10%/Lv) -&gt; 50%</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7617,6 +8979,12 @@
           <t>Heal an enemy's HP to decrease its physical and magic defense.</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>DEF: -5% -&gt; -6% -&gt; -7% -&gt; -8% -&gt; -10% (L1-5 Max)   |   Magic defense: -10% -&gt; -15%
+Accuracy: 80% -&gt; 90%   |   HP recovery: 35 -&gt; 25   |   Turns: 3   |   TP: 18 (+2-4/Lv) -&gt; 32</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7637,6 +9005,12 @@
           <t>Pierce to the back row with a raw magic attack and RES-based extra damage.</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Pwr: 100 -&gt; 130 -&gt; 160 -&gt; 200 -&gt; 240 -&gt; 280 -&gt; 320 -&gt; 370 -&gt; 420 -&gt; 480 (L10)
+Accuracy: 80% (+1-2%/Lv) -&gt; 90%   |   TP Cost: 30 (+4/Lv) -&gt; 66   |   Speed: 0.85x</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7657,6 +9031,12 @@
           <t>Deal enormous damage to one enemy that possesses life. Low chance of instakill.</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Pwr: 360 (+40-50/Lv) -&gt; 740   |   Accuracy: 76% (+1%/Lv)   |   Instakill: 12%
+TP Cost: 32 -&gt; 35 -&gt; 38 -&gt; 41 -&gt; 44 -&gt; 47 -&gt; 50 -&gt; 52 -&gt; 54 -&gt; 56   |   Speed: 1.2x</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7677,6 +9057,12 @@
           <t>Either heal or damage an enemy based on the enemy's HP.</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Maximum damage UP   |   Maximum heal UP
+TP Cost: 30 -&gt; 33 -&gt; 36 -&gt; 39 -&gt; 42 (L1-5 Max)   |   Speed: 1.5x   |   Chant: 0.84x -&gt; 0.8x</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -7697,6 +9083,12 @@
           <t>Actual course of action</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -7717,6 +9109,12 @@
           <t>Actual course of action</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -7737,6 +9135,12 @@
           <t>Actual course of action</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -7757,6 +9161,12 @@
           <t>Actual course of action</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -7777,6 +9187,12 @@
           <t>Actual course of action</t>
         </is>
       </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>dummy
+dummy</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -7797,6 +9213,7 @@
           <t>Deal direct damage back to attacker.</t>
         </is>
       </c>
+      <c r="E242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -7817,6 +9234,11 @@
           <t>ATK bonus with sword equipped.</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -7837,6 +9259,11 @@
           <t>ATK bonus with axe equipped.</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -7857,6 +9284,11 @@
           <t>ATK bonus with dagger equipped.</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -7877,6 +9309,11 @@
           <t>ATK bonus with mace equipped.</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -7897,6 +9334,11 @@
           <t>ATK bonus with lance equipped.</t>
         </is>
       </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -7917,6 +9359,11 @@
           <t>ATK bonus with bow equipped.</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -7937,6 +9384,11 @@
           <t>ATK bonus with katana equipped.</t>
         </is>
       </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -7957,6 +9409,11 @@
           <t>ATK bonus with projectile weapon equipped.</t>
         </is>
       </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>ATK bonus: 5% -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -7977,6 +9434,11 @@
           <t>ATK bonus with whip equipped.</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>ATK bonus: 3% -&gt; 5 -&gt; 7 -&gt; 9 -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 15 -&gt; 16 -&gt; 17% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -7997,6 +9459,11 @@
           <t>ATK bonus with fan equipped.</t>
         </is>
       </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>ATK bonus: 5% -&gt; 7 -&gt; 9 -&gt; 11 -&gt; 13 -&gt; 15 -&gt; 17 -&gt; 18 -&gt; 19 -&gt; 20% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8017,6 +9484,11 @@
           <t>ATK bonus for all weapons.</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>ATK bonus: 2% -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 12% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8037,6 +9509,11 @@
           <t>Magic attack power bonus.</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Magic attack bonus: 6% -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8057,6 +9534,12 @@
           <t>Healing magic bonus. Raises healing cap.</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>HP recovery bonus: 8% -&gt; 10 -&gt; 12 -&gt; 14 -&gt; 16 -&gt; 18 -&gt; 20 -&gt; 22 -&gt; 24 -&gt; 26% (L10)
+Heal Cap: +10% -&gt; +20 -&gt; +30 -&gt; +40 -&gt; +50 -&gt; +60 -&gt; +70 -&gt; +80 -&gt; +90 -&gt; +100%</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8077,6 +9560,11 @@
           <t>Recover HP every turn during battle.</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>HP recovery: 2% -&gt; 4% -&gt; 6% -&gt; 8% -&gt; 10% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8097,6 +9585,11 @@
           <t>Slightly recover HP every turn during battle.</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>HP recovery: 1% -&gt; 2% -&gt; 3% -&gt; 4% -&gt; 5% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8117,6 +9610,11 @@
           <t>Recover TP every turn during battle.</t>
         </is>
       </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>TP recovery: 3 -&gt; 6 -&gt; 9 -&gt; 12 -&gt; 16 (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8137,6 +9635,11 @@
           <t>Slightly recover TP every turn during battle.</t>
         </is>
       </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>TP recovery: 1 -&gt; 3 -&gt; 5 -&gt; 7 -&gt; 9 (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8157,6 +9660,11 @@
           <t>Raise resistance to all elements.</t>
         </is>
       </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Elemental resistance: 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12 -&gt; 13 -&gt; 14 -&gt; 15 (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8177,6 +9685,11 @@
           <t>Occasionally counterattack after receiving physical damage.</t>
         </is>
       </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Counterattack rate: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8197,6 +9710,11 @@
           <t>Occasionally parry and counterattack when targeted by an enemy.</t>
         </is>
       </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Activation rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8217,6 +9735,11 @@
           <t>Occasionally attack twice when attacking normally.</t>
         </is>
       </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Double attack rate: 9% -&gt; 12% -&gt; 15% -&gt; 18% -&gt; 21% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8237,6 +9760,11 @@
           <t>Occasionally attack thrice when attacking normally.</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Triple attack rate: 5% -&gt; 8% -&gt; 11% -&gt; 14% -&gt; 17% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8257,6 +9785,11 @@
           <t>Increase evasion rate against stab attacks.</t>
         </is>
       </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Evasion rate: 20% -&gt; 24% -&gt; 28% -&gt; 32% -&gt; 36% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8277,6 +9810,11 @@
           <t>Occasionally parry when receiving long-range attacks.</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Activation rate: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -8297,6 +9835,11 @@
           <t>Occasionally survive at 1 HP after being dealt fatal damage.</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Survival rate: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -8317,6 +9860,11 @@
           <t>Occasionally Defend automatically when receiving physical attacks.</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Auto-guard rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -8337,6 +9885,11 @@
           <t>Can equip two one-handed weapons at the same time.</t>
         </is>
       </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Sub-weapon ATK: 30% -&gt; 35 -&gt; 40 -&gt; 45 -&gt; 50 -&gt; 54 -&gt; 58 -&gt; 62 -&gt; 68 -&gt; 72% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -8357,6 +9910,11 @@
           <t>Convert some received damage to TP.</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>TP conversion: 4% -&gt; 8% -&gt; 12% -&gt; 16% -&gt; 20% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -8377,6 +9935,11 @@
           <t>Occasionally instakill when inflicting a critical hit.</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Activation rate: 8% -&gt; 11% -&gt; 14% -&gt; 17% -&gt; 20% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -8397,6 +9960,11 @@
           <t>With bow equipped, occasionally halt an enemy's action.</t>
         </is>
       </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Activation rate: 2% -&gt; 3% -&gt; 4% -&gt; 5% -&gt; 6% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -8417,6 +9985,11 @@
           <t>With bow equipped, occasionally attack again after an ally's attack.</t>
         </is>
       </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Activation rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -8437,6 +10010,11 @@
           <t>Gain increased speed based on missing HP.</t>
         </is>
       </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Speed increase: 15% -&gt; 16% -&gt; 17% -&gt; 18% -&gt; 20% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -8457,6 +10035,11 @@
           <t>Debuff an enemy when they inflict short-range damage.</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Number of possible debuffs: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 (L6)</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -8477,6 +10060,11 @@
           <t>Increase ATK while inflicted with status ailments.</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>ATK: +15% -&gt; +18% -&gt; +21% -&gt; +24% -&gt; +27% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -8497,6 +10085,7 @@
           <t>Nullify the effects of enemy Dark Auras.</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -8517,6 +10106,7 @@
           <t>No longer suffer counterattacks from enemies.</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -8537,6 +10127,11 @@
           <t>Decrease physical damage to the back row when using a shield in the front row.</t>
         </is>
       </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Physical damage: -6% -&gt; -7% -&gt; -8% -&gt; -9% -&gt; -10% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -8557,6 +10152,11 @@
           <t>Occasionally nullify physical damage.</t>
         </is>
       </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Activation rate: 8% -&gt; 9% -&gt; 10% -&gt; 11% -&gt; 12% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -8577,6 +10177,11 @@
           <t>Automatically heal inflicted status ailments at the start of each turn.</t>
         </is>
       </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>LvUp: Can cure poison &gt; paralysis &gt; silence &gt; freeze &gt; sleep &gt; slow</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -8597,6 +10202,11 @@
           <t>Briefly increase ATK and DEX when HP drops below 50%.</t>
         </is>
       </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>ATK/DEX: +10% -&gt; +11% -&gt; +12% -&gt; +13% -&gt; +15% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -8617,6 +10227,11 @@
           <t>Make it harder for chants, songs, and dances to be interrupted.</t>
         </is>
       </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>LvUp: Interruption rate DOWN</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -8637,6 +10252,11 @@
           <t>Reduce chant time.</t>
         </is>
       </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Chant time: -8% -&gt; -11% -&gt; -14% -&gt; -17% -&gt; -20% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -8657,6 +10277,11 @@
           <t>Reduce TP Cost in battle.</t>
         </is>
       </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>TP Cost reduction: 10% -&gt; 15% -&gt; 20% -&gt; 25% -&gt; 30% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -8677,6 +10302,11 @@
           <t>Heighten magic accuracy.</t>
         </is>
       </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Accuracy: 3% -&gt; 5% -&gt; 7% -&gt; 9% -&gt; 12% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -8697,6 +10327,11 @@
           <t>Limit enemies' preemptive attacks.</t>
         </is>
       </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Enemy preemptive attack rate: -20% -&gt; -28% -&gt; -36% -&gt; -44% -&gt; -50% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -8717,6 +10352,11 @@
           <t>Increase party's preemptive attack rate.</t>
         </is>
       </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Preemptive attack rate: 8% -&gt; 11% -&gt; 14% -&gt; 17% -&gt; 20% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -8737,6 +10377,11 @@
           <t>May escape from battle more easily.</t>
         </is>
       </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Battle escape rate: 20% -&gt; 25% -&gt; 30% -&gt; 35% -&gt; 40% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -8757,6 +10402,11 @@
           <t>Increase the enemies' item drop rate.</t>
         </is>
       </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Item drop rate: 4% -&gt; 6% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -8777,6 +10427,11 @@
           <t>Increase the amount of money the enemies drop.</t>
         </is>
       </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Gold drop rate: 25% -&gt; 50% -&gt; 75% -&gt; 100% -&gt; 125% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -8797,6 +10452,11 @@
           <t>Sometimes pick up items while moving around the dungeons.</t>
         </is>
       </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Found item quality: 1 -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -8817,6 +10477,12 @@
           <t>Party's HP and TP is restored slightly after a battle.</t>
         </is>
       </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Post-battle HP: 6% -&gt; 7% -&gt; 8% -&gt; 10% -&gt; 12% (L1-5 Max)
+Post-battle TP: 3% -&gt; 4% -&gt; 5% -&gt; 7% -&gt; 9%</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -8837,6 +10503,11 @@
           <t>Occasionally keep disposable items after using them in battle.</t>
         </is>
       </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Item keep rate: 25% -&gt; 27% -&gt; 29% -&gt; 32% -&gt; 35% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -8857,6 +10528,11 @@
           <t>Increase the effects of HP and TP recovery items during battle.</t>
         </is>
       </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Item effects: 10% -&gt; 20 -&gt; 30 -&gt; 40 -&gt; 50 -&gt; 60 -&gt; 70 -&gt; 80 -&gt; 90 -&gt; 100% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -8877,6 +10553,11 @@
           <t>Become capable of performing two songs at once.</t>
         </is>
       </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -8897,6 +10578,11 @@
           <t>Become capable of performing two dances at once.</t>
         </is>
       </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -8917,6 +10603,11 @@
           <t>Become capable of controlling two dolls at once.</t>
         </is>
       </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Speed: 6% -&gt; 9% -&gt; 12% -&gt; 15% -&gt; 18% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -8937,6 +10628,11 @@
           <t>Increase doll power with the strength of the equipped Sealbook.</t>
         </is>
       </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Sealbook ability: +15% -&gt; +18% -&gt; +21% -&gt; +24% -&gt; +27% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -8957,6 +10653,11 @@
           <t>Increased effects for all maid skills.</t>
         </is>
       </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Maid skill bonus: 1% -&gt; 2 -&gt; 3 -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -8977,6 +10678,11 @@
           <t>Increased effects for all songs.</t>
         </is>
       </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Singing skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -8997,6 +10703,11 @@
           <t>Increased effects for all dances.</t>
         </is>
       </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Dancing skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -9017,6 +10728,11 @@
           <t>Increased effects for all doll skills.</t>
         </is>
       </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Doll skill bonus: 3% -&gt; 4 -&gt; 5 -&gt; 6 -&gt; 7 -&gt; 8 -&gt; 9 -&gt; 10 -&gt; 11 -&gt; 12% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -9037,6 +10753,11 @@
           <t>Occasionally attack twice when attacking normally.</t>
         </is>
       </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Double attack rate: 20% -&gt; 21 -&gt; 22 -&gt; 23 -&gt; 24 -&gt; 25 -&gt; 26 -&gt; 28 -&gt; 30 -&gt; 32% (L10)</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -9057,6 +10778,11 @@
           <t>Reduce chant time for songs.</t>
         </is>
       </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Song chant time: -10% -&gt; -11 -&gt; -12 -&gt; -13 -&gt; -14 -&gt; -15 -&gt; -16 -&gt; -17 -&gt; -18 -&gt; -20%</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -9077,6 +10803,11 @@
           <t>Reduce purchase and identification prices at shops.</t>
         </is>
       </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Negotiation rate: 10% -&gt; 14% -&gt; 18% -&gt; 22% -&gt; 25% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -9097,6 +10828,11 @@
           <t>Mesmerize enemies, causing them to occasionally do nothing.</t>
         </is>
       </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Occurrence rate: 3% -&gt; 4% -&gt; 5% -&gt; 6% -&gt; 7% (L1-5 Max)</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -9117,6 +10853,7 @@
           <t>Nullify first hit of battle against user (does not work for status ailments).</t>
         </is>
       </c>
+      <c r="E308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -9137,6 +10874,7 @@
           <t>Heighten the probability of beneficial results for random effect skills.</t>
         </is>
       </c>
+      <c r="E309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -9157,6 +10895,7 @@
           <t>Whip skill. Strike back with a normal attack before a targeted attack hits you.</t>
         </is>
       </c>
+      <c r="E310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -9177,6 +10916,7 @@
           <t>Occasionally get the first action regardless of speed.</t>
         </is>
       </c>
+      <c r="E311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -9197,6 +10937,7 @@
           <t>Occasionally land critical hits with offensive spells.</t>
         </is>
       </c>
+      <c r="E312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -9217,6 +10958,7 @@
           <t>Increase doll summon duration by 1 turn.</t>
         </is>
       </c>
+      <c r="E313" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data_tables/guide_text.xlsx
+++ b/data_tables/guide_text.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,153 +491,187 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>equip_section</t>
+          <t>enchantments_title</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>#### Usable Equipment</t>
+          <t># Equipment Enchantments</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Equipment compatibility based on class usability flags.</t>
+          <t>Reference for equipment enchantments, scaling per equipped piece, stacking rules, and caps verified in the game engine.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>formulas_title</t>
+          <t>equip_section</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t># Battle Formulas</t>
+          <t>#### Usable Equipment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reference for combat mathematics, damage functions, turn order calculations, and status ailment checks in Dungeon Travelers 2-2. Every formula represents the exact logic executed by the game engine.</t>
+          <t>Equipment compatibility based on class usability flags.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>growth_section</t>
+          <t>equipment_title</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>#### Stat Growth</t>
+          <t># Equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Reference for weapons, armor, accessories, weapon recovery delay ranks, and equipment upgrade rates in Dungeon Travelers 2-2.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>modifier_section</t>
+          <t>formulas_title</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>#### Weapon Specialty Modifiers</t>
+          <t># Battle Formulas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Equipping a specialized weapon, shield, or accessory grants a percentage bonus to all non-zero stats on that piece: `int((character_stat + piece_stat) * modifier)`.</t>
+          <t>Reference for combat mathematics, damage functions, turn order calculations, and status ailment checks in Dungeon Travelers 2-2. Every formula represents the exact logic executed by the game engine.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>overview_section</t>
+          <t>growth_section</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>#### Class Overview</t>
+          <t>#### Stat Growth</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>readme_glossary</t>
+          <t>modifier_section</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>## Glossary</t>
+          <t>#### Weapon Specialty Modifiers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Core combat parameters, calculations, and mechanical terms used throughout this guide.</t>
+          <t>Equipping a specialized weapon, shield, or accessory grants a percentage bonus to all non-zero stats on that piece: `int((character_stat + piece_stat) * modifier)`.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>readme_how_to_read</t>
+          <t>overview_section</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>## How to Read the Tables</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Stat tables record raw class attributes at milestone levels from 1 to 99. Modifiers operate additively unless specified by game logic. Equipment usability lists weapon classes and defensive gear categories supported by internal compatibility bitmasks.</t>
+          <t>#### Class Overview</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>readme_title</t>
+          <t>readme_glossary</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t># Dungeon Travelers 2-2 Reference Guide (Vanilla)</t>
+          <t>## Glossary</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Player reference documentation for the original English PC release of Dungeon Travelers 2-2. All data, mechanics, and formulas are compiled directly from the original game files.</t>
+          <t>Core combat parameters, calculations, and mechanical terms used throughout this guide.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>skills_section</t>
+          <t>readme_how_to_read</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>#### Learned Skills</t>
+          <t>## How to Read the Tables</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Stat tables record raw class attributes at milestone levels from 1 to 99. Modifiers operate additively unless specified by game logic. Equipment usability lists weapon classes and defensive gear categories supported by internal compatibility bitmasks.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>readme_title</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t># Dungeon Travelers 2-2 Reference Guide (Vanilla)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Player reference documentation for the original English PC release of Dungeon Travelers 2-2. All data, mechanics, and formulas are compiled directly from the original game files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>skills_section</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>#### Learned Skills</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>skills_title</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t># Skills</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Reference for all skills learned by player classes, including category, TP and SP costs, action speed, cast speed, target, range, and exact numerical scaling across all levels.</t>
         </is>
@@ -654,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,490 +706,670 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>agi</t>
+          <t>accessory</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>Accessory</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>atk</t>
+          <t>agi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>AGI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>base_class</t>
+          <t>armor</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Base Class</t>
+          <t>Armor</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bonus</t>
+          <t>atk</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Modifier</t>
+          <t>ATK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cast_factor</t>
+          <t>base_class</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chant Speed</t>
+          <t>Base Class</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>body_armor</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Body Armor</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>character</t>
+          <t>bonus</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Modifier</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>classes</t>
+          <t>cap</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Classes</t>
+          <t>Cap / Limit</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>cast_factor</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Count</t>
+          <t>Chant Speed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>def</t>
+          <t>category</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>Type</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>character</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Effect &amp; Scaling</t>
+          <t>Character</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dex</t>
+          <t>classes</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DEX</t>
+          <t>Classes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>equipment_type</t>
+          <t>count</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Equipment Type</t>
+          <t>Count</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gear_categories</t>
+          <t>def</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Defensive Gear</t>
+          <t>DEF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hp</t>
+          <t>delay_mult</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Delay Mult</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>delay_rank</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>Delay Rank</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>join_point</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Join Point</t>
+          <t>Effect &amp; Scaling</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Level</t>
+          <t>DEX</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>line</t>
+          <t>enchantment</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Enchantment</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>max_lv</t>
+          <t>equipment_type</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Max Lv</t>
+          <t>Equipment Type</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>overview</t>
+          <t>gear_categories</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Class Overview</t>
+          <t>Defensive Gear</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>profile</t>
+          <t>headgear</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Combat Role &amp; Profile</t>
+          <t>Headgear</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>range</t>
+          <t>hp</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>HP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rank</t>
+          <t>innate_enchants</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Innate Enchants</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ranks</t>
+          <t>int</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rank Scaling</t>
+          <t>INT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>res</t>
+          <t>join_point</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RES</t>
+          <t>Join Point</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>level</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Promotion Route</t>
+          <t>Level</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>skill</t>
+          <t>line</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Line</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>slot</t>
+          <t>magnitude</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Slot</t>
+          <t>Value / Scaling</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sp_cost</t>
+          <t>max_lv</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Total SP</t>
+          <t>Max Lv</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>speed_factor</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Action Speed</t>
+          <t>Class Overview</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>start_exp</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Starting EXP</t>
+          <t>Combat Role &amp; Profile</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>start_level</t>
+          <t>range</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Starting Lv</t>
+          <t>Range</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>target</t>
+          <t>rank</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Rank</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tier</t>
+          <t>ranks</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tier</t>
+          <t>Rank Scaling</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>tp</t>
+          <t>res</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>RES</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tp_cost</t>
+          <t>route</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TP Cost</t>
+          <t>Promotion Route</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>turns</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Shield</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>unique_skill</t>
+          <t>skill</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Unique Skill</t>
+          <t>Skill</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>slot</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Slot</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>sp_cost</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Total SP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>speed_factor</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Action Speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Stacking Rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>start_exp</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Starting EXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>start_level</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Starting Lv</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tp_cost</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>TP Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>turns</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>two_handed</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2-Handed</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>unique_skill</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unique Skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>upgrade_rate</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Upgrade Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>weapon_types</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Weapon Types</t>
         </is>

--- a/data_tables/guide_text.xlsx
+++ b/data_tables/guide_text.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,6 +674,91 @@
       <c r="C16" t="inlineStr">
         <is>
           <t>Reference for all skills learned by player classes, including category, TP and SP costs, action speed, cast speed, target, range, and exact numerical scaling across all levels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>enemies_title</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t># Enemies</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Catalog of all enemies in Dungeon Travelers 2-2 organized by habitat, including combat stats, element resistances, ailment immunities, attack skills, and drop rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>bosses_title</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t># Boss Encounters</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Reference for fixed story and postgame boss encounters, including combat stats, elemental resistances, attack repertoires, and complete AI behavior scripts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>summons_title</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t># Grand Sealbook Summons</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Reference for all 35 Grand Sealbook summons, detailing stat growth factors, attack repertoires, AI weights, and passive enchantments across all three forms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mercenaries_title</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t># Mercenaries (Guest Allies)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Reference for all hireable mercenaries at the Tavern, including unlock requirements, hiring costs, contract lengths, growth stages, combat stats, attack repertoires, and AI scripts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>progression_title</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t># Game Progression</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Experience and skill point curves from Level 1 to 99, crown reset stat bonus milestones, and encounter level ranges across all dungeon floors.</t>
         </is>
       </c>
     </row>
@@ -688,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1372,6 +1457,474 @@
       <c r="B57" t="inlineStr">
         <is>
           <t>Weapon Types</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>EXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>race</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>resistances</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Resistances</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>immunities</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Immunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>drops</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Item Drops</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>equip_drop</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Equipment Drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>snack</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>steal</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Steal</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>attacks</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Attacks</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>passives</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Passives</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ai_script</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>AI Behavior</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>opening</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Opening Actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>action_sets</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Action Sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>slash</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Slash</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>stab</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Stab</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>bash</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Bash</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>earth</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Earth</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>lightning</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>speed</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>unlock</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Unlock Point</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>factors</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Stat Multipliers</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>req_exp</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Required EXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>total_exp</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Cumulative EXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>sp_gain</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SP Gained</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>dungeon</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Dungeon</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>floor</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>enemy_levels</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Random Enemy Levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>boss_levels</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Boss Encounters</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>bonus_stats</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Bonus Stats</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>reset_level</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Reset Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>cap_info</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Stat Cap</t>
         </is>
       </c>
     </row>
